--- a/Documents/Product Catalog/Full Product Catalog/Office Furniture.xlsx
+++ b/Documents/Product Catalog/Full Product Catalog/Office Furniture.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\Talukder Furniture\Documents\Product Catalog\Full Product Catalog\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\By Raj\Talukder Furniture\Documents\Product Catalog\Full Product Catalog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B20ABBE-3C47-4849-B1AE-561C5179C6CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD6D7660-FC0B-4B0A-B0FB-9C913AAD664F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3375" yWindow="3375" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Office Furniture (2)" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1713" uniqueCount="593">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1713" uniqueCount="633">
   <si>
     <t>Talukder Furniture Ltd.</t>
   </si>
@@ -657,9 +657,6 @@
     <t>TFL-DUO-201 LB</t>
   </si>
   <si>
-    <t>Mobile Drawer Unit</t>
-  </si>
-  <si>
     <t>Drawer Units</t>
   </si>
   <si>
@@ -808,9 +805,6 @@
     <t>TFL-SRO-201 LB</t>
   </si>
   <si>
-    <t>Side Rack</t>
-  </si>
-  <si>
     <t>Storage &amp; Organizers</t>
   </si>
   <si>
@@ -1149,9 +1143,6 @@
     <t>TFL-HCO-201 LB</t>
   </si>
   <si>
-    <t>Hanging File Cabinet</t>
-  </si>
-  <si>
     <t>L 2120 x W 1880 x H 850 mm</t>
   </si>
   <si>
@@ -2913,9 +2904,6 @@
   </si>
   <si>
     <t>TFL-RTO-201 LB</t>
-  </si>
-  <si>
-    <t>Reception Table</t>
   </si>
   <si>
     <t>Reception Desks</t>
@@ -3358,6 +3346,138 @@
 Prevent Scratches: Use felt pads under lamps, vases, and decorative items to avoid scraping the finish
 Manage Humidity: Wood expands and contracts with moisture. Aim to keep your indoor humidity levels steady.
 </t>
+  </si>
+  <si>
+    <t>পদ্ম Sr. Executive Table</t>
+  </si>
+  <si>
+    <t>শিল্পিক Sr. Executive Table</t>
+  </si>
+  <si>
+    <t>অরণ্য Sr. Executive Table</t>
+  </si>
+  <si>
+    <t>চারুলতা Sr. Executive Table</t>
+  </si>
+  <si>
+    <t>অম্বরী Sr. Executive Table</t>
+  </si>
+  <si>
+    <t>পুঞ্জিকা Sr. Executive Table</t>
+  </si>
+  <si>
+    <t>পদ্ম Mobile Drawer Unit</t>
+  </si>
+  <si>
+    <t>শিল্পিক Mobile Drawer Unit</t>
+  </si>
+  <si>
+    <t>অরণ্য Mobile Drawer Unit</t>
+  </si>
+  <si>
+    <t>চারুলতা Mobile Drawer Unit</t>
+  </si>
+  <si>
+    <t>অম্বরী Hanging Drawer</t>
+  </si>
+  <si>
+    <t>পুঞ্জিকা Hanging Drawer</t>
+  </si>
+  <si>
+    <t>পদ্ম Side Rack</t>
+  </si>
+  <si>
+    <t>শিল্পিক Side Rack</t>
+  </si>
+  <si>
+    <t>অরণ্য Side Rack</t>
+  </si>
+  <si>
+    <t>চারুলতা Side Rack</t>
+  </si>
+  <si>
+    <t>অম্বরী Side Rack</t>
+  </si>
+  <si>
+    <t>পুঞ্জিকা Side Rack</t>
+  </si>
+  <si>
+    <t>পদ্ম Computer Table</t>
+  </si>
+  <si>
+    <t>শিল্পিক Computer Table</t>
+  </si>
+  <si>
+    <t>অরণ্য Computer Table</t>
+  </si>
+  <si>
+    <t>চারুলতা Computer Table</t>
+  </si>
+  <si>
+    <t>অম্বরী Computer Table</t>
+  </si>
+  <si>
+    <t>পুঞ্জিকা Computer Table</t>
+  </si>
+  <si>
+    <t>পদ্ম Multipurpose Shelf</t>
+  </si>
+  <si>
+    <t>শিল্পিক Multipurpose Shelf</t>
+  </si>
+  <si>
+    <t>অরণ্য Multipurpose Shelf</t>
+  </si>
+  <si>
+    <t>চারুলতা Multipurpose Shelf</t>
+  </si>
+  <si>
+    <t>পদ্ম Hanging File Cabinet</t>
+  </si>
+  <si>
+    <t>শিল্পিক Hanging File Cabinet</t>
+  </si>
+  <si>
+    <t>পদ্ম Conference Table</t>
+  </si>
+  <si>
+    <t>শিল্পিক Conference Table</t>
+  </si>
+  <si>
+    <t>অরণ্য Conference Table</t>
+  </si>
+  <si>
+    <t>চারুলতা Conference Table</t>
+  </si>
+  <si>
+    <t>পদ্ম Podium</t>
+  </si>
+  <si>
+    <t>অরণ্য Podium</t>
+  </si>
+  <si>
+    <t>পদ্ম Workstation</t>
+  </si>
+  <si>
+    <t>শিল্পিক Workstation</t>
+  </si>
+  <si>
+    <t>অরণ্য Workstation</t>
+  </si>
+  <si>
+    <t>চারুলতা Workstation</t>
+  </si>
+  <si>
+    <t>পদ্ম Reception Table</t>
+  </si>
+  <si>
+    <t>শিল্পিক Reception Table</t>
+  </si>
+  <si>
+    <t>অরণ্য Reception Table</t>
+  </si>
+  <si>
+    <t>চারুলতা Reception Table</t>
   </si>
 </sst>
 </file>
@@ -3891,41 +4011,44 @@
     <xf numFmtId="1" fontId="4" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="10" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="1" fontId="10" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="1" fontId="10" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3937,12 +4060,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3978,40 +4095,43 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="10" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="10" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="10" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -12424,81 +12544,81 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:48" ht="39.950000000000003" customHeight="1">
-      <c r="B1" s="60" t="s">
+      <c r="B1" s="99" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
-      <c r="K1" s="60"/>
-      <c r="L1" s="60"/>
-      <c r="M1" s="60"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="99"/>
+      <c r="F1" s="99"/>
+      <c r="G1" s="99"/>
+      <c r="H1" s="99"/>
+      <c r="I1" s="99"/>
+      <c r="J1" s="99"/>
+      <c r="K1" s="99"/>
+      <c r="L1" s="99"/>
+      <c r="M1" s="99"/>
       <c r="N1" s="6"/>
       <c r="O1" s="5"/>
       <c r="P1" s="5"/>
     </row>
     <row r="2" spans="2:48" ht="39.950000000000003" customHeight="1">
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="100" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="61"/>
-      <c r="M2" s="61"/>
+      <c r="C2" s="100"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="100"/>
+      <c r="K2" s="100"/>
+      <c r="L2" s="100"/>
+      <c r="M2" s="100"/>
       <c r="N2" s="7"/>
       <c r="O2" s="5"/>
       <c r="P2" s="5"/>
     </row>
     <row r="3" spans="2:48" ht="50.1" customHeight="1">
-      <c r="B3" s="66" t="s">
+      <c r="B3" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="62" t="s">
+      <c r="C3" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="62" t="s">
+      <c r="D3" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="79" t="s">
+      <c r="E3" s="78" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="79" t="s">
+      <c r="F3" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="62" t="s">
+      <c r="G3" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62" t="s">
+      <c r="H3" s="64"/>
+      <c r="I3" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="79" t="s">
+      <c r="J3" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="K3" s="62" t="s">
+      <c r="K3" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="L3" s="62"/>
-      <c r="M3" s="62"/>
-      <c r="N3" s="62" t="s">
+      <c r="L3" s="64"/>
+      <c r="M3" s="64"/>
+      <c r="N3" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="62" t="s">
+      <c r="O3" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="P3" s="62" t="s">
+      <c r="P3" s="64" t="s">
         <v>13</v>
       </c>
       <c r="U3" s="5"/>
@@ -12531,19 +12651,19 @@
       <c r="AV3" s="5"/>
     </row>
     <row r="4" spans="2:48" ht="33.200000000000003" customHeight="1">
-      <c r="B4" s="67"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="80"/>
+      <c r="B4" s="94"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="79"/>
+      <c r="F4" s="79"/>
       <c r="G4" s="8" t="s">
         <v>14</v>
       </c>
       <c r="H4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="62"/>
-      <c r="J4" s="80"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="79"/>
       <c r="K4" s="9" t="s">
         <v>16</v>
       </c>
@@ -12553,9 +12673,9 @@
       <c r="M4" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="N4" s="62"/>
-      <c r="O4" s="62"/>
-      <c r="P4" s="62"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="64"/>
       <c r="U4" s="5"/>
       <c r="V4" s="5"/>
       <c r="W4" s="5"/>
@@ -12593,7 +12713,7 @@
         <v>20</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>21</v>
+        <v>589</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="11" t="s">
@@ -12667,7 +12787,7 @@
         <v>31</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>21</v>
+        <v>590</v>
       </c>
       <c r="E6" s="12"/>
       <c r="F6" s="11" t="s">
@@ -12741,7 +12861,7 @@
         <v>33</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>21</v>
+        <v>591</v>
       </c>
       <c r="E7" s="12"/>
       <c r="F7" s="11" t="s">
@@ -12815,7 +12935,7 @@
         <v>36</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>21</v>
+        <v>592</v>
       </c>
       <c r="E8" s="12"/>
       <c r="F8" s="11" t="s">
@@ -12889,7 +13009,7 @@
         <v>41</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>21</v>
+        <v>593</v>
       </c>
       <c r="E9" s="12"/>
       <c r="F9" s="11" t="s">
@@ -12963,7 +13083,7 @@
         <v>45</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>21</v>
+        <v>594</v>
       </c>
       <c r="E10" s="12"/>
       <c r="F10" s="11" t="s">
@@ -14658,20 +14778,20 @@
       <c r="AV32" s="5"/>
     </row>
     <row r="33" spans="2:48" ht="50.1" customHeight="1">
-      <c r="B33" s="63" t="s">
+      <c r="B33" s="90" t="s">
         <v>131</v>
       </c>
-      <c r="C33" s="64"/>
-      <c r="D33" s="64"/>
-      <c r="E33" s="64"/>
-      <c r="F33" s="64"/>
-      <c r="G33" s="64"/>
-      <c r="H33" s="64"/>
-      <c r="I33" s="64"/>
-      <c r="J33" s="64"/>
-      <c r="K33" s="64"/>
-      <c r="L33" s="64"/>
-      <c r="M33" s="65"/>
+      <c r="C33" s="91"/>
+      <c r="D33" s="91"/>
+      <c r="E33" s="91"/>
+      <c r="F33" s="91"/>
+      <c r="G33" s="91"/>
+      <c r="H33" s="91"/>
+      <c r="I33" s="91"/>
+      <c r="J33" s="91"/>
+      <c r="K33" s="91"/>
+      <c r="L33" s="91"/>
+      <c r="M33" s="92"/>
       <c r="N33" s="19" t="s">
         <v>27</v>
       </c>
@@ -14718,7 +14838,7 @@
         <v>133</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>134</v>
+        <v>595</v>
       </c>
       <c r="E34" s="12"/>
       <c r="F34" s="11" t="s">
@@ -14728,13 +14848,13 @@
         <v>23</v>
       </c>
       <c r="H34" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="I34" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="I34" s="15" t="s">
+      <c r="J34" s="11" t="s">
         <v>136</v>
-      </c>
-      <c r="J34" s="11" t="s">
-        <v>137</v>
       </c>
       <c r="K34" s="16">
         <f t="shared" ref="K34:K40" si="1">L34*(1-0.22)</f>
@@ -14750,7 +14870,7 @@
         <v>27</v>
       </c>
       <c r="O34" s="21" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="P34" s="20" t="s">
         <v>29</v>
@@ -14789,10 +14909,10 @@
         <v>30</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>134</v>
+        <v>596</v>
       </c>
       <c r="E35" s="12"/>
       <c r="F35" s="11" t="s">
@@ -14802,13 +14922,13 @@
         <v>23</v>
       </c>
       <c r="H35" s="14" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I35" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="J35" s="11" t="s">
         <v>140</v>
-      </c>
-      <c r="J35" s="11" t="s">
-        <v>141</v>
       </c>
       <c r="K35" s="16">
         <f t="shared" si="1"/>
@@ -14824,7 +14944,7 @@
         <v>27</v>
       </c>
       <c r="O35" s="21" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P35" s="20" t="s">
         <v>29</v>
@@ -14863,10 +14983,10 @@
         <v>31</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>134</v>
+        <v>597</v>
       </c>
       <c r="E36" s="12"/>
       <c r="F36" s="11" t="s">
@@ -14876,10 +14996,10 @@
         <v>23</v>
       </c>
       <c r="H36" s="14" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I36" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J36" s="11" t="s">
         <v>83</v>
@@ -14898,7 +15018,7 @@
         <v>27</v>
       </c>
       <c r="O36" s="21" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="P36" s="20" t="s">
         <v>29</v>
@@ -14937,10 +15057,10 @@
         <v>32</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>134</v>
+        <v>598</v>
       </c>
       <c r="E37" s="12"/>
       <c r="F37" s="11" t="s">
@@ -14950,10 +15070,10 @@
         <v>23</v>
       </c>
       <c r="H37" s="14" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I37" s="15" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J37" s="11" t="s">
         <v>83</v>
@@ -14972,7 +15092,7 @@
         <v>27</v>
       </c>
       <c r="O37" s="21" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P37" s="20" t="s">
         <v>29</v>
@@ -15011,10 +15131,10 @@
         <v>33</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>149</v>
+        <v>599</v>
       </c>
       <c r="E38" s="12"/>
       <c r="F38" s="11" t="s">
@@ -15024,13 +15144,13 @@
         <v>23</v>
       </c>
       <c r="H38" s="14" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I38" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="J38" s="11" t="s">
         <v>150</v>
-      </c>
-      <c r="J38" s="11" t="s">
-        <v>151</v>
       </c>
       <c r="K38" s="16">
         <f t="shared" si="1"/>
@@ -15046,7 +15166,7 @@
         <v>27</v>
       </c>
       <c r="O38" s="21" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P38" s="20" t="s">
         <v>29</v>
@@ -15085,10 +15205,10 @@
         <v>34</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>149</v>
+        <v>600</v>
       </c>
       <c r="E39" s="12"/>
       <c r="F39" s="11" t="s">
@@ -15098,10 +15218,10 @@
         <v>23</v>
       </c>
       <c r="H39" s="14" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I39" s="15" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J39" s="11" t="s">
         <v>83</v>
@@ -15120,7 +15240,7 @@
         <v>27</v>
       </c>
       <c r="O39" s="21" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="P39" s="20" t="s">
         <v>29</v>
@@ -15159,10 +15279,10 @@
         <v>35</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E40" s="12"/>
       <c r="F40" s="11" t="s">
@@ -15172,13 +15292,13 @@
         <v>23</v>
       </c>
       <c r="H40" s="14" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I40" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="J40" s="11" t="s">
         <v>157</v>
-      </c>
-      <c r="J40" s="11" t="s">
-        <v>158</v>
       </c>
       <c r="K40" s="16">
         <f t="shared" si="1"/>
@@ -15194,7 +15314,7 @@
         <v>27</v>
       </c>
       <c r="O40" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P40" s="20" t="s">
         <v>29</v>
@@ -15229,25 +15349,25 @@
       <c r="AV40" s="5"/>
     </row>
     <row r="41" spans="2:48" ht="50.1" customHeight="1">
-      <c r="B41" s="63" t="s">
-        <v>160</v>
-      </c>
-      <c r="C41" s="64"/>
-      <c r="D41" s="64"/>
-      <c r="E41" s="64"/>
-      <c r="F41" s="64"/>
-      <c r="G41" s="64"/>
-      <c r="H41" s="64"/>
-      <c r="I41" s="64"/>
-      <c r="J41" s="64"/>
-      <c r="K41" s="64"/>
-      <c r="L41" s="64"/>
-      <c r="M41" s="65"/>
+      <c r="B41" s="90" t="s">
+        <v>159</v>
+      </c>
+      <c r="C41" s="91"/>
+      <c r="D41" s="91"/>
+      <c r="E41" s="91"/>
+      <c r="F41" s="91"/>
+      <c r="G41" s="91"/>
+      <c r="H41" s="91"/>
+      <c r="I41" s="91"/>
+      <c r="J41" s="91"/>
+      <c r="K41" s="91"/>
+      <c r="L41" s="91"/>
+      <c r="M41" s="92"/>
       <c r="N41" s="19" t="s">
         <v>27</v>
       </c>
       <c r="O41" s="21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="P41" s="20" t="s">
         <v>29</v>
@@ -15286,10 +15406,10 @@
         <v>36</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>163</v>
+        <v>601</v>
       </c>
       <c r="E42" s="11"/>
       <c r="F42" s="11" t="s">
@@ -15299,13 +15419,13 @@
         <v>23</v>
       </c>
       <c r="H42" s="22" t="s">
+        <v>162</v>
+      </c>
+      <c r="I42" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="J42" s="11" t="s">
         <v>164</v>
-      </c>
-      <c r="I42" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="J42" s="11" t="s">
-        <v>166</v>
       </c>
       <c r="K42" s="16">
         <f t="shared" ref="K42:K47" si="2">L42*(1-0.22)</f>
@@ -15321,7 +15441,7 @@
         <v>27</v>
       </c>
       <c r="O42" s="21" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="P42" s="20" t="s">
         <v>29</v>
@@ -15360,10 +15480,10 @@
         <v>37</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>163</v>
+        <v>602</v>
       </c>
       <c r="E43" s="12"/>
       <c r="F43" s="11" t="s">
@@ -15373,13 +15493,13 @@
         <v>23</v>
       </c>
       <c r="H43" s="22" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I43" s="11" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="J43" s="11" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="K43" s="16">
         <f t="shared" si="2"/>
@@ -15395,7 +15515,7 @@
         <v>27</v>
       </c>
       <c r="O43" s="21" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="P43" s="20" t="s">
         <v>29</v>
@@ -15434,10 +15554,10 @@
         <v>38</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>163</v>
+        <v>603</v>
       </c>
       <c r="E44" s="12"/>
       <c r="F44" s="11" t="s">
@@ -15447,13 +15567,13 @@
         <v>23</v>
       </c>
       <c r="H44" s="22" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I44" s="11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J44" s="11" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="K44" s="16">
         <f t="shared" si="2"/>
@@ -15469,7 +15589,7 @@
         <v>27</v>
       </c>
       <c r="O44" s="21" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="P44" s="20" t="s">
         <v>29</v>
@@ -15508,10 +15628,10 @@
         <v>39</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>163</v>
+        <v>604</v>
       </c>
       <c r="E45" s="12"/>
       <c r="F45" s="11" t="s">
@@ -15521,10 +15641,10 @@
         <v>23</v>
       </c>
       <c r="H45" s="22" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="J45" s="11" t="s">
         <v>26</v>
@@ -15543,7 +15663,7 @@
         <v>27</v>
       </c>
       <c r="O45" s="21" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="P45" s="20" t="s">
         <v>29</v>
@@ -15582,10 +15702,10 @@
         <v>40</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>163</v>
+        <v>605</v>
       </c>
       <c r="E46" s="12"/>
       <c r="F46" s="11" t="s">
@@ -15595,13 +15715,13 @@
         <v>23</v>
       </c>
       <c r="H46" s="22" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I46" s="11" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="K46" s="16">
         <f t="shared" si="2"/>
@@ -15617,7 +15737,7 @@
         <v>27</v>
       </c>
       <c r="O46" s="21" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="P46" s="20" t="s">
         <v>29</v>
@@ -15656,10 +15776,10 @@
         <v>41</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>163</v>
+        <v>606</v>
       </c>
       <c r="E47" s="12"/>
       <c r="F47" s="11" t="s">
@@ -15669,13 +15789,13 @@
         <v>23</v>
       </c>
       <c r="H47" s="22" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I47" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="J47" s="11" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="K47" s="16">
         <f t="shared" si="2"/>
@@ -15691,7 +15811,7 @@
         <v>27</v>
       </c>
       <c r="O47" s="21" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="P47" s="20" t="s">
         <v>29</v>
@@ -15727,7 +15847,7 @@
     </row>
     <row r="48" spans="2:48" ht="50.1" customHeight="1">
       <c r="B48" s="23" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C48" s="24"/>
       <c r="D48" s="24"/>
@@ -15744,7 +15864,7 @@
         <v>27</v>
       </c>
       <c r="O48" s="21" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="P48" s="20" t="s">
         <v>29</v>
@@ -15783,26 +15903,26 @@
         <v>42</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>186</v>
+        <v>607</v>
       </c>
       <c r="E49" s="12"/>
       <c r="F49" s="11" t="s">
         <v>22</v>
       </c>
       <c r="G49" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="H49" s="22" t="s">
+        <v>188</v>
+      </c>
+      <c r="I49" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="H49" s="22" t="s">
-        <v>190</v>
-      </c>
-      <c r="I49" s="11" t="s">
-        <v>191</v>
-      </c>
       <c r="J49" s="26" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="K49" s="16">
         <f t="shared" ref="K49:K54" si="3">L49*(1-0.22)</f>
@@ -15818,7 +15938,7 @@
         <v>27</v>
       </c>
       <c r="O49" s="21" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="P49" s="20" t="s">
         <v>29</v>
@@ -15857,23 +15977,23 @@
         <v>43</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>186</v>
+        <v>608</v>
       </c>
       <c r="E50" s="11"/>
       <c r="F50" s="11" t="s">
         <v>22</v>
       </c>
       <c r="G50" s="11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H50" s="22" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="I50" s="11" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="J50" s="11" t="s">
         <v>42</v>
@@ -15892,7 +16012,7 @@
         <v>27</v>
       </c>
       <c r="O50" s="21" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="P50" s="20" t="s">
         <v>29</v>
@@ -15931,23 +16051,23 @@
         <v>44</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>186</v>
+        <v>609</v>
       </c>
       <c r="E51" s="12"/>
       <c r="F51" s="11" t="s">
         <v>22</v>
       </c>
       <c r="G51" s="11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H51" s="22" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="I51" s="11" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="J51" s="11" t="s">
         <v>42</v>
@@ -15966,7 +16086,7 @@
         <v>27</v>
       </c>
       <c r="O51" s="21" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="P51" s="20" t="s">
         <v>29</v>
@@ -16005,26 +16125,26 @@
         <v>45</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>186</v>
+        <v>610</v>
       </c>
       <c r="E52" s="12"/>
       <c r="F52" s="11" t="s">
         <v>22</v>
       </c>
       <c r="G52" s="11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H52" s="22" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="I52" s="11" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J52" s="26" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="K52" s="16">
         <f t="shared" si="3"/>
@@ -16040,7 +16160,7 @@
         <v>27</v>
       </c>
       <c r="O52" s="21" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="P52" s="20" t="s">
         <v>29</v>
@@ -16079,26 +16199,26 @@
         <v>46</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>186</v>
+        <v>611</v>
       </c>
       <c r="E53" s="12"/>
       <c r="F53" s="11" t="s">
         <v>22</v>
       </c>
       <c r="G53" s="11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H53" s="22" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="I53" s="11" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="J53" s="26" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="K53" s="16">
         <f t="shared" si="3"/>
@@ -16114,7 +16234,7 @@
         <v>27</v>
       </c>
       <c r="O53" s="21" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="P53" s="20" t="s">
         <v>29</v>
@@ -16153,26 +16273,26 @@
         <v>47</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>186</v>
+        <v>612</v>
       </c>
       <c r="E54" s="12"/>
       <c r="F54" s="11" t="s">
         <v>22</v>
       </c>
       <c r="G54" s="11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H54" s="22" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="J54" s="27" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="K54" s="16">
         <f t="shared" si="3"/>
@@ -16188,7 +16308,7 @@
         <v>27</v>
       </c>
       <c r="O54" s="21" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="P54" s="20" t="s">
         <v>29</v>
@@ -16223,25 +16343,25 @@
       <c r="AV54" s="5"/>
     </row>
     <row r="55" spans="2:48" ht="50.1" customHeight="1">
-      <c r="B55" s="63" t="s">
-        <v>208</v>
-      </c>
-      <c r="C55" s="64"/>
-      <c r="D55" s="64"/>
-      <c r="E55" s="64"/>
-      <c r="F55" s="64"/>
-      <c r="G55" s="64"/>
-      <c r="H55" s="64"/>
-      <c r="I55" s="64"/>
-      <c r="J55" s="64"/>
-      <c r="K55" s="64"/>
-      <c r="L55" s="64"/>
-      <c r="M55" s="65"/>
+      <c r="B55" s="90" t="s">
+        <v>206</v>
+      </c>
+      <c r="C55" s="91"/>
+      <c r="D55" s="91"/>
+      <c r="E55" s="91"/>
+      <c r="F55" s="91"/>
+      <c r="G55" s="91"/>
+      <c r="H55" s="91"/>
+      <c r="I55" s="91"/>
+      <c r="J55" s="91"/>
+      <c r="K55" s="91"/>
+      <c r="L55" s="91"/>
+      <c r="M55" s="92"/>
       <c r="N55" s="19" t="s">
         <v>27</v>
       </c>
       <c r="O55" s="21" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="P55" s="20" t="s">
         <v>29</v>
@@ -16280,26 +16400,26 @@
         <v>48</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>208</v>
+        <v>613</v>
       </c>
       <c r="E56" s="12"/>
       <c r="F56" s="11" t="s">
         <v>22</v>
       </c>
       <c r="G56" s="11" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="H56" s="22" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I56" s="11" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="J56" s="26" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="K56" s="16">
         <f>L56*(1-0.22)</f>
@@ -16315,7 +16435,7 @@
         <v>27</v>
       </c>
       <c r="O56" s="21" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="P56" s="20" t="s">
         <v>29</v>
@@ -16354,23 +16474,23 @@
         <v>49</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>208</v>
+        <v>614</v>
       </c>
       <c r="E57" s="12"/>
       <c r="F57" s="11" t="s">
         <v>22</v>
       </c>
       <c r="G57" s="11" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="H57" s="22" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J57" s="11" t="s">
         <v>42</v>
@@ -16389,7 +16509,7 @@
         <v>27</v>
       </c>
       <c r="O57" s="21" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="P57" s="20" t="s">
         <v>29</v>
@@ -16428,26 +16548,26 @@
         <v>50</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>208</v>
+        <v>615</v>
       </c>
       <c r="E58" s="11"/>
       <c r="F58" s="11" t="s">
         <v>22</v>
       </c>
       <c r="G58" s="11" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="H58" s="22" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="J58" s="26" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="K58" s="16">
         <f>L58*(1-0.22)</f>
@@ -16463,7 +16583,7 @@
         <v>27</v>
       </c>
       <c r="O58" s="21" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="P58" s="20" t="s">
         <v>29</v>
@@ -16502,26 +16622,26 @@
         <v>51</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>208</v>
+        <v>616</v>
       </c>
       <c r="E59" s="12"/>
       <c r="F59" s="11" t="s">
         <v>22</v>
       </c>
       <c r="G59" s="11" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="H59" s="22" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="J59" s="26" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="K59" s="16">
         <f>L59*(1-0.22)</f>
@@ -16537,7 +16657,7 @@
         <v>27</v>
       </c>
       <c r="O59" s="21" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="P59" s="20" t="s">
         <v>29</v>
@@ -16572,25 +16692,25 @@
       <c r="AV59" s="5"/>
     </row>
     <row r="60" spans="2:48" ht="50.1" customHeight="1">
-      <c r="B60" s="63" t="s">
-        <v>223</v>
-      </c>
-      <c r="C60" s="64"/>
-      <c r="D60" s="64"/>
-      <c r="E60" s="64"/>
-      <c r="F60" s="64"/>
-      <c r="G60" s="64"/>
-      <c r="H60" s="64"/>
-      <c r="I60" s="64"/>
-      <c r="J60" s="64"/>
-      <c r="K60" s="64"/>
-      <c r="L60" s="64"/>
-      <c r="M60" s="65"/>
+      <c r="B60" s="90" t="s">
+        <v>221</v>
+      </c>
+      <c r="C60" s="91"/>
+      <c r="D60" s="91"/>
+      <c r="E60" s="91"/>
+      <c r="F60" s="91"/>
+      <c r="G60" s="91"/>
+      <c r="H60" s="91"/>
+      <c r="I60" s="91"/>
+      <c r="J60" s="91"/>
+      <c r="K60" s="91"/>
+      <c r="L60" s="91"/>
+      <c r="M60" s="92"/>
       <c r="N60" s="19" t="s">
         <v>27</v>
       </c>
       <c r="O60" s="21" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="P60" s="20" t="s">
         <v>29</v>
@@ -16629,26 +16749,26 @@
         <v>52</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>226</v>
+        <v>617</v>
       </c>
       <c r="E61" s="12"/>
       <c r="F61" s="11" t="s">
         <v>22</v>
       </c>
       <c r="G61" s="11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H61" s="22" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="K61" s="16">
         <f>L61*(1-0.22)</f>
@@ -16664,7 +16784,7 @@
         <v>27</v>
       </c>
       <c r="O61" s="21" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="P61" s="20" t="s">
         <v>29</v>
@@ -16703,26 +16823,26 @@
         <v>53</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>226</v>
+        <v>618</v>
       </c>
       <c r="E62" s="12"/>
       <c r="F62" s="11" t="s">
         <v>22</v>
       </c>
       <c r="G62" s="11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H62" s="22" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="K62" s="16">
         <f>L62*(1-0.22)</f>
@@ -16738,7 +16858,7 @@
         <v>27</v>
       </c>
       <c r="O62" s="21" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="P62" s="20" t="s">
         <v>29</v>
@@ -16777,26 +16897,26 @@
         <v>54</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>226</v>
+        <v>618</v>
       </c>
       <c r="E63" s="12"/>
       <c r="F63" s="11" t="s">
         <v>22</v>
       </c>
       <c r="G63" s="11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H63" s="22" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="K63" s="16">
         <f>L63*(1-0.22)</f>
@@ -16812,7 +16932,7 @@
         <v>27</v>
       </c>
       <c r="O63" s="21" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="P63" s="20" t="s">
         <v>29</v>
@@ -16847,25 +16967,25 @@
       <c r="AV63" s="5"/>
     </row>
     <row r="64" spans="2:48" ht="50.1" customHeight="1">
-      <c r="B64" s="63" t="s">
-        <v>233</v>
-      </c>
-      <c r="C64" s="64"/>
-      <c r="D64" s="64"/>
-      <c r="E64" s="64"/>
-      <c r="F64" s="64"/>
-      <c r="G64" s="64"/>
-      <c r="H64" s="64"/>
-      <c r="I64" s="64"/>
-      <c r="J64" s="64"/>
-      <c r="K64" s="64"/>
-      <c r="L64" s="64"/>
-      <c r="M64" s="65"/>
+      <c r="B64" s="90" t="s">
+        <v>230</v>
+      </c>
+      <c r="C64" s="91"/>
+      <c r="D64" s="91"/>
+      <c r="E64" s="91"/>
+      <c r="F64" s="91"/>
+      <c r="G64" s="91"/>
+      <c r="H64" s="91"/>
+      <c r="I64" s="91"/>
+      <c r="J64" s="91"/>
+      <c r="K64" s="91"/>
+      <c r="L64" s="91"/>
+      <c r="M64" s="92"/>
       <c r="N64" s="19" t="s">
         <v>27</v>
       </c>
       <c r="O64" s="21" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="P64" s="20" t="s">
         <v>29</v>
@@ -16904,10 +17024,10 @@
         <v>55</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>233</v>
+        <v>619</v>
       </c>
       <c r="E65" s="11"/>
       <c r="F65" s="11" t="s">
@@ -16917,13 +17037,13 @@
         <v>23</v>
       </c>
       <c r="H65" s="22" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="I65" s="11" t="s">
         <v>78</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K65" s="16">
         <f t="shared" ref="K65:K70" si="4">L65*(1-0.22)</f>
@@ -16939,7 +17059,7 @@
         <v>27</v>
       </c>
       <c r="O65" s="21" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="P65" s="20" t="s">
         <v>29</v>
@@ -16978,10 +17098,10 @@
         <v>56</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>233</v>
+        <v>619</v>
       </c>
       <c r="E66" s="12"/>
       <c r="F66" s="11" t="s">
@@ -16991,13 +17111,13 @@
         <v>23</v>
       </c>
       <c r="H66" s="22" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K66" s="16">
         <f t="shared" si="4"/>
@@ -17013,7 +17133,7 @@
         <v>27</v>
       </c>
       <c r="O66" s="21" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="P66" s="20" t="s">
         <v>29</v>
@@ -17052,10 +17172,10 @@
         <v>57</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>233</v>
+        <v>619</v>
       </c>
       <c r="E67" s="12"/>
       <c r="F67" s="11" t="s">
@@ -17065,13 +17185,13 @@
         <v>23</v>
       </c>
       <c r="H67" s="22" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="I67" s="11" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K67" s="16">
         <f t="shared" si="4"/>
@@ -17087,7 +17207,7 @@
         <v>27</v>
       </c>
       <c r="O67" s="21" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="P67" s="20" t="s">
         <v>29</v>
@@ -17126,10 +17246,10 @@
         <v>58</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>233</v>
+        <v>620</v>
       </c>
       <c r="E68" s="12"/>
       <c r="F68" s="11" t="s">
@@ -17139,13 +17259,13 @@
         <v>23</v>
       </c>
       <c r="H68" s="22" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="K68" s="16">
         <f t="shared" si="4"/>
@@ -17161,7 +17281,7 @@
         <v>27</v>
       </c>
       <c r="O68" s="21" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="P68" s="20" t="s">
         <v>29</v>
@@ -17172,10 +17292,10 @@
         <v>59</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>233</v>
+        <v>621</v>
       </c>
       <c r="E69" s="11"/>
       <c r="F69" s="11" t="s">
@@ -17185,13 +17305,13 @@
         <v>23</v>
       </c>
       <c r="H69" s="22" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K69" s="16">
         <f t="shared" si="4"/>
@@ -17207,7 +17327,7 @@
         <v>27</v>
       </c>
       <c r="O69" s="21" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="P69" s="20" t="s">
         <v>29</v>
@@ -17218,10 +17338,10 @@
         <v>60</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>233</v>
+        <v>622</v>
       </c>
       <c r="E70" s="12"/>
       <c r="F70" s="11" t="s">
@@ -17231,13 +17351,13 @@
         <v>23</v>
       </c>
       <c r="H70" s="22" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="K70" s="16">
         <f t="shared" si="4"/>
@@ -17253,62 +17373,62 @@
         <v>27</v>
       </c>
       <c r="O70" s="21" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="P70" s="20" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="71" spans="2:48" ht="50.1" customHeight="1">
-      <c r="B71" s="63" t="s">
-        <v>251</v>
-      </c>
-      <c r="C71" s="64"/>
-      <c r="D71" s="64"/>
-      <c r="E71" s="64"/>
-      <c r="F71" s="64"/>
-      <c r="G71" s="64"/>
-      <c r="H71" s="64"/>
-      <c r="I71" s="64"/>
-      <c r="J71" s="64"/>
-      <c r="K71" s="64"/>
-      <c r="L71" s="64"/>
-      <c r="M71" s="65"/>
+      <c r="B71" s="90" t="s">
+        <v>248</v>
+      </c>
+      <c r="C71" s="91"/>
+      <c r="D71" s="91"/>
+      <c r="E71" s="91"/>
+      <c r="F71" s="91"/>
+      <c r="G71" s="91"/>
+      <c r="H71" s="91"/>
+      <c r="I71" s="91"/>
+      <c r="J71" s="91"/>
+      <c r="K71" s="91"/>
+      <c r="L71" s="91"/>
+      <c r="M71" s="92"/>
       <c r="N71" s="19" t="s">
         <v>27</v>
       </c>
       <c r="O71" s="21" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="P71" s="20" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="72" spans="2:48" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
-      <c r="B72" s="68">
+      <c r="B72" s="95">
         <v>61</v>
       </c>
-      <c r="C72" s="72" t="s">
+      <c r="C72" s="73" t="s">
+        <v>250</v>
+      </c>
+      <c r="D72" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="E72" s="80"/>
+      <c r="F72" s="73" t="s">
+        <v>252</v>
+      </c>
+      <c r="G72" s="73" t="s">
+        <v>23</v>
+      </c>
+      <c r="H72" s="67" t="s">
+        <v>248</v>
+      </c>
+      <c r="I72" s="69" t="s">
         <v>253</v>
       </c>
-      <c r="D72" s="28" t="s">
+      <c r="J72" s="28" t="s">
         <v>254</v>
-      </c>
-      <c r="E72" s="81"/>
-      <c r="F72" s="72" t="s">
-        <v>255</v>
-      </c>
-      <c r="G72" s="72" t="s">
-        <v>23</v>
-      </c>
-      <c r="H72" s="91" t="s">
-        <v>251</v>
-      </c>
-      <c r="I72" s="95" t="s">
-        <v>256</v>
-      </c>
-      <c r="J72" s="28" t="s">
-        <v>257</v>
       </c>
       <c r="K72" s="29">
         <f t="shared" ref="K72:K85" si="5">L72*(1-22%)</f>
@@ -17322,7 +17442,7 @@
         <v>27</v>
       </c>
       <c r="O72" s="21" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P72" s="20" t="s">
         <v>29</v>
@@ -17333,18 +17453,18 @@
       <c r="T72" s="32"/>
     </row>
     <row r="73" spans="2:48" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
-      <c r="B73" s="69"/>
-      <c r="C73" s="73"/>
+      <c r="B73" s="96"/>
+      <c r="C73" s="74"/>
       <c r="D73" s="28" t="s">
-        <v>259</v>
-      </c>
-      <c r="E73" s="82"/>
-      <c r="F73" s="89"/>
-      <c r="G73" s="73"/>
-      <c r="H73" s="92"/>
-      <c r="I73" s="89"/>
+        <v>256</v>
+      </c>
+      <c r="E73" s="81"/>
+      <c r="F73" s="70"/>
+      <c r="G73" s="74"/>
+      <c r="H73" s="68"/>
+      <c r="I73" s="70"/>
       <c r="J73" s="28" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="K73" s="29">
         <f t="shared" si="5"/>
@@ -17358,7 +17478,7 @@
         <v>27</v>
       </c>
       <c r="O73" s="21" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="P73" s="20" t="s">
         <v>29</v>
@@ -17369,30 +17489,30 @@
       <c r="T73" s="32"/>
     </row>
     <row r="74" spans="2:48" ht="80.099999999999994" customHeight="1">
-      <c r="B74" s="70">
+      <c r="B74" s="97">
         <v>62</v>
       </c>
-      <c r="C74" s="74" t="s">
+      <c r="C74" s="75" t="s">
+        <v>258</v>
+      </c>
+      <c r="D74" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="E74" s="82"/>
+      <c r="F74" s="75" t="s">
+        <v>259</v>
+      </c>
+      <c r="G74" s="75" t="s">
+        <v>23</v>
+      </c>
+      <c r="H74" s="65" t="s">
+        <v>248</v>
+      </c>
+      <c r="I74" s="71" t="s">
+        <v>260</v>
+      </c>
+      <c r="J74" s="60" t="s">
         <v>261</v>
-      </c>
-      <c r="D74" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="E74" s="83"/>
-      <c r="F74" s="74" t="s">
-        <v>262</v>
-      </c>
-      <c r="G74" s="74" t="s">
-        <v>23</v>
-      </c>
-      <c r="H74" s="93" t="s">
-        <v>251</v>
-      </c>
-      <c r="I74" s="96" t="s">
-        <v>263</v>
-      </c>
-      <c r="J74" s="97" t="s">
-        <v>264</v>
       </c>
       <c r="K74" s="33">
         <f t="shared" si="5"/>
@@ -17408,24 +17528,24 @@
         <v>27</v>
       </c>
       <c r="O74" s="21" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="P74" s="20" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="75" spans="2:48" ht="80.099999999999994" customHeight="1">
-      <c r="B75" s="71"/>
-      <c r="C75" s="75"/>
+      <c r="B75" s="98"/>
+      <c r="C75" s="76"/>
       <c r="D75" s="11" t="s">
-        <v>259</v>
-      </c>
-      <c r="E75" s="84"/>
-      <c r="F75" s="90"/>
-      <c r="G75" s="75"/>
-      <c r="H75" s="94"/>
-      <c r="I75" s="90"/>
-      <c r="J75" s="98"/>
+        <v>256</v>
+      </c>
+      <c r="E75" s="83"/>
+      <c r="F75" s="72"/>
+      <c r="G75" s="76"/>
+      <c r="H75" s="66"/>
+      <c r="I75" s="72"/>
+      <c r="J75" s="61"/>
       <c r="K75" s="33">
         <f t="shared" si="5"/>
         <v>13650</v>
@@ -17440,37 +17560,37 @@
         <v>27</v>
       </c>
       <c r="O75" s="21" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="P75" s="20" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="76" spans="2:48" ht="80.099999999999994" customHeight="1">
-      <c r="B76" s="70">
+      <c r="B76" s="97">
         <v>63</v>
       </c>
-      <c r="C76" s="74" t="s">
-        <v>267</v>
+      <c r="C76" s="75" t="s">
+        <v>264</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="E76" s="83"/>
-      <c r="F76" s="74" t="s">
-        <v>268</v>
-      </c>
-      <c r="G76" s="74" t="s">
+        <v>251</v>
+      </c>
+      <c r="E76" s="82"/>
+      <c r="F76" s="75" t="s">
+        <v>265</v>
+      </c>
+      <c r="G76" s="75" t="s">
         <v>23</v>
       </c>
-      <c r="H76" s="93" t="s">
-        <v>251</v>
-      </c>
-      <c r="I76" s="96" t="s">
-        <v>263</v>
-      </c>
-      <c r="J76" s="97" t="s">
-        <v>269</v>
+      <c r="H76" s="65" t="s">
+        <v>248</v>
+      </c>
+      <c r="I76" s="71" t="s">
+        <v>260</v>
+      </c>
+      <c r="J76" s="60" t="s">
+        <v>266</v>
       </c>
       <c r="K76" s="33">
         <f t="shared" si="5"/>
@@ -17486,24 +17606,24 @@
         <v>27</v>
       </c>
       <c r="O76" s="21" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="P76" s="20" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="77" spans="2:48" ht="80.099999999999994" customHeight="1">
-      <c r="B77" s="71"/>
-      <c r="C77" s="75"/>
+      <c r="B77" s="98"/>
+      <c r="C77" s="76"/>
       <c r="D77" s="11" t="s">
-        <v>259</v>
-      </c>
-      <c r="E77" s="84"/>
-      <c r="F77" s="90"/>
-      <c r="G77" s="75"/>
-      <c r="H77" s="94"/>
-      <c r="I77" s="90"/>
-      <c r="J77" s="98"/>
+        <v>256</v>
+      </c>
+      <c r="E77" s="83"/>
+      <c r="F77" s="72"/>
+      <c r="G77" s="76"/>
+      <c r="H77" s="66"/>
+      <c r="I77" s="72"/>
+      <c r="J77" s="61"/>
       <c r="K77" s="33">
         <f t="shared" si="5"/>
         <v>17160</v>
@@ -17518,37 +17638,37 @@
         <v>27</v>
       </c>
       <c r="O77" s="21" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="P77" s="20" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="78" spans="2:48" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
-      <c r="B78" s="68">
+      <c r="B78" s="95">
         <v>64</v>
       </c>
-      <c r="C78" s="72" t="s">
-        <v>272</v>
+      <c r="C78" s="73" t="s">
+        <v>269</v>
       </c>
       <c r="D78" s="28" t="s">
-        <v>254</v>
-      </c>
-      <c r="E78" s="85"/>
-      <c r="F78" s="72" t="s">
-        <v>273</v>
-      </c>
-      <c r="G78" s="72" t="s">
+        <v>251</v>
+      </c>
+      <c r="E78" s="84"/>
+      <c r="F78" s="73" t="s">
+        <v>270</v>
+      </c>
+      <c r="G78" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="H78" s="91" t="s">
-        <v>251</v>
-      </c>
-      <c r="I78" s="95" t="s">
-        <v>256</v>
-      </c>
-      <c r="J78" s="99" t="s">
-        <v>269</v>
+      <c r="H78" s="67" t="s">
+        <v>248</v>
+      </c>
+      <c r="I78" s="69" t="s">
+        <v>253</v>
+      </c>
+      <c r="J78" s="62" t="s">
+        <v>266</v>
       </c>
       <c r="K78" s="29">
         <f t="shared" si="5"/>
@@ -17562,7 +17682,7 @@
         <v>27</v>
       </c>
       <c r="O78" s="21" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="P78" s="20" t="s">
         <v>29</v>
@@ -17573,17 +17693,17 @@
       <c r="T78" s="32"/>
     </row>
     <row r="79" spans="2:48" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
-      <c r="B79" s="69"/>
-      <c r="C79" s="73"/>
+      <c r="B79" s="96"/>
+      <c r="C79" s="74"/>
       <c r="D79" s="28" t="s">
-        <v>259</v>
-      </c>
-      <c r="E79" s="86"/>
-      <c r="F79" s="89"/>
-      <c r="G79" s="73"/>
-      <c r="H79" s="92"/>
-      <c r="I79" s="89"/>
-      <c r="J79" s="100"/>
+        <v>256</v>
+      </c>
+      <c r="E79" s="85"/>
+      <c r="F79" s="70"/>
+      <c r="G79" s="74"/>
+      <c r="H79" s="68"/>
+      <c r="I79" s="70"/>
+      <c r="J79" s="63"/>
       <c r="K79" s="29">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -17596,7 +17716,7 @@
         <v>27</v>
       </c>
       <c r="O79" s="21" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="P79" s="20" t="s">
         <v>29</v>
@@ -17607,30 +17727,30 @@
       <c r="T79" s="32"/>
     </row>
     <row r="80" spans="2:48" ht="80.099999999999994" customHeight="1">
-      <c r="B80" s="70">
+      <c r="B80" s="97">
         <v>65</v>
       </c>
-      <c r="C80" s="74" t="s">
-        <v>276</v>
+      <c r="C80" s="75" t="s">
+        <v>273</v>
       </c>
       <c r="D80" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="E80" s="87"/>
-      <c r="F80" s="74" t="s">
-        <v>277</v>
-      </c>
-      <c r="G80" s="74" t="s">
+        <v>251</v>
+      </c>
+      <c r="E80" s="86"/>
+      <c r="F80" s="75" t="s">
+        <v>274</v>
+      </c>
+      <c r="G80" s="75" t="s">
         <v>23</v>
       </c>
-      <c r="H80" s="93" t="s">
-        <v>251</v>
-      </c>
-      <c r="I80" s="96" t="s">
-        <v>263</v>
-      </c>
-      <c r="J80" s="97" t="s">
-        <v>269</v>
+      <c r="H80" s="65" t="s">
+        <v>248</v>
+      </c>
+      <c r="I80" s="71" t="s">
+        <v>260</v>
+      </c>
+      <c r="J80" s="60" t="s">
+        <v>266</v>
       </c>
       <c r="K80" s="33">
         <f t="shared" si="5"/>
@@ -17646,24 +17766,24 @@
         <v>27</v>
       </c>
       <c r="O80" s="21" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="P80" s="20" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="81" spans="2:20" ht="80.099999999999994" customHeight="1">
-      <c r="B81" s="71"/>
-      <c r="C81" s="75"/>
+      <c r="B81" s="98"/>
+      <c r="C81" s="76"/>
       <c r="D81" s="11" t="s">
-        <v>259</v>
-      </c>
-      <c r="E81" s="88"/>
-      <c r="F81" s="90"/>
-      <c r="G81" s="75"/>
-      <c r="H81" s="94"/>
-      <c r="I81" s="90"/>
-      <c r="J81" s="98"/>
+        <v>256</v>
+      </c>
+      <c r="E81" s="87"/>
+      <c r="F81" s="72"/>
+      <c r="G81" s="76"/>
+      <c r="H81" s="66"/>
+      <c r="I81" s="72"/>
+      <c r="J81" s="61"/>
       <c r="K81" s="33">
         <f t="shared" si="5"/>
         <v>11778</v>
@@ -17678,37 +17798,37 @@
         <v>27</v>
       </c>
       <c r="O81" s="21" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="P81" s="20" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="82" spans="2:20" ht="80.099999999999994" customHeight="1">
-      <c r="B82" s="70">
+      <c r="B82" s="97">
         <v>66</v>
       </c>
-      <c r="C82" s="74" t="s">
-        <v>280</v>
+      <c r="C82" s="75" t="s">
+        <v>277</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="E82" s="87"/>
-      <c r="F82" s="74" t="s">
-        <v>281</v>
-      </c>
-      <c r="G82" s="74" t="s">
+        <v>251</v>
+      </c>
+      <c r="E82" s="86"/>
+      <c r="F82" s="75" t="s">
+        <v>278</v>
+      </c>
+      <c r="G82" s="75" t="s">
         <v>23</v>
       </c>
-      <c r="H82" s="93" t="s">
-        <v>251</v>
-      </c>
-      <c r="I82" s="96" t="s">
-        <v>263</v>
-      </c>
-      <c r="J82" s="97" t="s">
-        <v>282</v>
+      <c r="H82" s="65" t="s">
+        <v>248</v>
+      </c>
+      <c r="I82" s="71" t="s">
+        <v>260</v>
+      </c>
+      <c r="J82" s="60" t="s">
+        <v>279</v>
       </c>
       <c r="K82" s="33">
         <f t="shared" si="5"/>
@@ -17724,24 +17844,24 @@
         <v>27</v>
       </c>
       <c r="O82" s="21" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="P82" s="20" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="83" spans="2:20" ht="80.099999999999994" customHeight="1">
-      <c r="B83" s="71"/>
-      <c r="C83" s="76"/>
+      <c r="B83" s="98"/>
+      <c r="C83" s="88"/>
       <c r="D83" s="11" t="s">
-        <v>259</v>
-      </c>
-      <c r="E83" s="88"/>
-      <c r="F83" s="90"/>
-      <c r="G83" s="75"/>
-      <c r="H83" s="94"/>
-      <c r="I83" s="90"/>
-      <c r="J83" s="98"/>
+        <v>256</v>
+      </c>
+      <c r="E83" s="87"/>
+      <c r="F83" s="72"/>
+      <c r="G83" s="76"/>
+      <c r="H83" s="66"/>
+      <c r="I83" s="72"/>
+      <c r="J83" s="61"/>
       <c r="K83" s="33">
         <f t="shared" si="5"/>
         <v>6396</v>
@@ -17756,37 +17876,37 @@
         <v>27</v>
       </c>
       <c r="O83" s="21" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="P83" s="20" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="84" spans="2:20" ht="80.099999999999994" customHeight="1">
-      <c r="B84" s="70">
+      <c r="B84" s="97">
         <v>67</v>
       </c>
-      <c r="C84" s="77" t="s">
-        <v>285</v>
+      <c r="C84" s="89" t="s">
+        <v>282</v>
       </c>
       <c r="D84" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="E84" s="87"/>
-      <c r="F84" s="74" t="s">
-        <v>286</v>
-      </c>
-      <c r="G84" s="74" t="s">
+        <v>251</v>
+      </c>
+      <c r="E84" s="86"/>
+      <c r="F84" s="75" t="s">
+        <v>283</v>
+      </c>
+      <c r="G84" s="75" t="s">
         <v>23</v>
       </c>
-      <c r="H84" s="93" t="s">
-        <v>251</v>
-      </c>
-      <c r="I84" s="96" t="s">
-        <v>263</v>
-      </c>
-      <c r="J84" s="97" t="s">
-        <v>282</v>
+      <c r="H84" s="65" t="s">
+        <v>248</v>
+      </c>
+      <c r="I84" s="71" t="s">
+        <v>260</v>
+      </c>
+      <c r="J84" s="60" t="s">
+        <v>279</v>
       </c>
       <c r="K84" s="33">
         <f t="shared" si="5"/>
@@ -17802,24 +17922,24 @@
         <v>27</v>
       </c>
       <c r="O84" s="21" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="P84" s="20" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="85" spans="2:20" ht="80.099999999999994" customHeight="1">
-      <c r="B85" s="71"/>
-      <c r="C85" s="77"/>
+      <c r="B85" s="98"/>
+      <c r="C85" s="89"/>
       <c r="D85" s="11" t="s">
-        <v>259</v>
-      </c>
-      <c r="E85" s="88"/>
-      <c r="F85" s="90"/>
-      <c r="G85" s="75"/>
-      <c r="H85" s="94"/>
-      <c r="I85" s="90"/>
-      <c r="J85" s="98"/>
+        <v>256</v>
+      </c>
+      <c r="E85" s="87"/>
+      <c r="F85" s="72"/>
+      <c r="G85" s="76"/>
+      <c r="H85" s="66"/>
+      <c r="I85" s="72"/>
+      <c r="J85" s="61"/>
       <c r="K85" s="33">
         <f t="shared" si="5"/>
         <v>9750</v>
@@ -17834,35 +17954,35 @@
         <v>27</v>
       </c>
       <c r="O85" s="21" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="P85" s="20" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="86" spans="2:20" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
-      <c r="B86" s="68">
+      <c r="B86" s="95">
         <v>68</v>
       </c>
-      <c r="C86" s="78" t="s">
-        <v>289</v>
+      <c r="C86" s="77" t="s">
+        <v>286</v>
       </c>
       <c r="D86" s="35"/>
-      <c r="E86" s="85"/>
-      <c r="F86" s="72" t="s">
-        <v>290</v>
-      </c>
-      <c r="G86" s="72" t="s">
+      <c r="E86" s="84"/>
+      <c r="F86" s="73" t="s">
+        <v>287</v>
+      </c>
+      <c r="G86" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="H86" s="91" t="s">
-        <v>251</v>
-      </c>
-      <c r="I86" s="72" t="s">
-        <v>291</v>
-      </c>
-      <c r="J86" s="99" t="s">
-        <v>282</v>
+      <c r="H86" s="67" t="s">
+        <v>248</v>
+      </c>
+      <c r="I86" s="73" t="s">
+        <v>288</v>
+      </c>
+      <c r="J86" s="62" t="s">
+        <v>279</v>
       </c>
       <c r="K86" s="29"/>
       <c r="L86" s="30">
@@ -17875,7 +17995,7 @@
         <v>27</v>
       </c>
       <c r="O86" s="21" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="P86" s="20" t="s">
         <v>29</v>
@@ -17886,17 +18006,17 @@
       <c r="T86" s="32"/>
     </row>
     <row r="87" spans="2:20" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
-      <c r="B87" s="69"/>
-      <c r="C87" s="78"/>
+      <c r="B87" s="96"/>
+      <c r="C87" s="77"/>
       <c r="D87" s="28" t="s">
-        <v>259</v>
-      </c>
-      <c r="E87" s="86"/>
-      <c r="F87" s="73"/>
-      <c r="G87" s="73"/>
-      <c r="H87" s="92"/>
-      <c r="I87" s="73"/>
-      <c r="J87" s="100"/>
+        <v>256</v>
+      </c>
+      <c r="E87" s="85"/>
+      <c r="F87" s="74"/>
+      <c r="G87" s="74"/>
+      <c r="H87" s="68"/>
+      <c r="I87" s="74"/>
+      <c r="J87" s="63"/>
       <c r="K87" s="29">
         <f>L87*(1-22%)</f>
         <v>0</v>
@@ -17909,7 +18029,7 @@
         <v>27</v>
       </c>
       <c r="O87" s="21" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="P87" s="20" t="s">
         <v>29</v>
@@ -17920,25 +18040,25 @@
       <c r="T87" s="32"/>
     </row>
     <row r="88" spans="2:20" ht="50.1" customHeight="1">
-      <c r="B88" s="63" t="s">
-        <v>251</v>
-      </c>
-      <c r="C88" s="64"/>
-      <c r="D88" s="64"/>
-      <c r="E88" s="64"/>
-      <c r="F88" s="64"/>
-      <c r="G88" s="64"/>
-      <c r="H88" s="64"/>
-      <c r="I88" s="64"/>
-      <c r="J88" s="64"/>
-      <c r="K88" s="64"/>
-      <c r="L88" s="64"/>
-      <c r="M88" s="65"/>
+      <c r="B88" s="90" t="s">
+        <v>248</v>
+      </c>
+      <c r="C88" s="91"/>
+      <c r="D88" s="91"/>
+      <c r="E88" s="91"/>
+      <c r="F88" s="91"/>
+      <c r="G88" s="91"/>
+      <c r="H88" s="91"/>
+      <c r="I88" s="91"/>
+      <c r="J88" s="91"/>
+      <c r="K88" s="91"/>
+      <c r="L88" s="91"/>
+      <c r="M88" s="92"/>
       <c r="N88" s="19" t="s">
         <v>27</v>
       </c>
       <c r="O88" s="21" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="P88" s="20" t="s">
         <v>29</v>
@@ -17949,26 +18069,26 @@
         <v>69</v>
       </c>
       <c r="C89" s="28" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D89" s="28" t="s">
-        <v>254</v>
-      </c>
-      <c r="E89" s="85"/>
+        <v>251</v>
+      </c>
+      <c r="E89" s="84"/>
       <c r="F89" s="28" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="G89" s="37" t="s">
         <v>23</v>
       </c>
       <c r="H89" s="38" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="I89" s="39" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J89" s="34" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="K89" s="40">
         <f>L89*(1-0.22)</f>
@@ -17984,7 +18104,7 @@
         <v>27</v>
       </c>
       <c r="O89" s="21" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="P89" s="20" t="s">
         <v>29</v>
@@ -17999,26 +18119,26 @@
         <v>70</v>
       </c>
       <c r="C90" s="28" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D90" s="28" t="s">
-        <v>299</v>
-      </c>
-      <c r="E90" s="86"/>
+        <v>296</v>
+      </c>
+      <c r="E90" s="85"/>
       <c r="F90" s="28" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="G90" s="28" t="s">
         <v>23</v>
       </c>
       <c r="H90" s="42" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="I90" s="28" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J90" s="34" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="K90" s="40">
         <f>L90*(1-0.22)</f>
@@ -18034,7 +18154,7 @@
         <v>27</v>
       </c>
       <c r="O90" s="21" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="P90" s="20" t="s">
         <v>29</v>
@@ -18045,25 +18165,25 @@
       <c r="T90" s="32"/>
     </row>
     <row r="91" spans="2:20" ht="50.1" customHeight="1">
-      <c r="B91" s="63" t="s">
-        <v>301</v>
-      </c>
-      <c r="C91" s="64"/>
-      <c r="D91" s="64"/>
-      <c r="E91" s="64"/>
-      <c r="F91" s="64"/>
-      <c r="G91" s="64"/>
-      <c r="H91" s="64"/>
-      <c r="I91" s="64"/>
-      <c r="J91" s="64"/>
-      <c r="K91" s="64"/>
-      <c r="L91" s="64"/>
-      <c r="M91" s="65"/>
+      <c r="B91" s="90" t="s">
+        <v>298</v>
+      </c>
+      <c r="C91" s="91"/>
+      <c r="D91" s="91"/>
+      <c r="E91" s="91"/>
+      <c r="F91" s="91"/>
+      <c r="G91" s="91"/>
+      <c r="H91" s="91"/>
+      <c r="I91" s="91"/>
+      <c r="J91" s="91"/>
+      <c r="K91" s="91"/>
+      <c r="L91" s="91"/>
+      <c r="M91" s="92"/>
       <c r="N91" s="19" t="s">
         <v>27</v>
       </c>
       <c r="O91" s="21" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="P91" s="20" t="s">
         <v>29</v>
@@ -18074,26 +18194,26 @@
         <v>71</v>
       </c>
       <c r="C92" s="28" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D92" s="28" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E92" s="41"/>
       <c r="F92" s="28" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="G92" s="28" t="s">
         <v>23</v>
       </c>
       <c r="H92" s="43" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I92" s="28" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J92" s="28" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="K92" s="44">
         <f t="shared" ref="K92:K111" si="6">L92*(1-22%)</f>
@@ -18109,7 +18229,7 @@
         <v>27</v>
       </c>
       <c r="O92" s="21" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="P92" s="20" t="s">
         <v>29</v>
@@ -18124,26 +18244,26 @@
         <v>72</v>
       </c>
       <c r="C93" s="28" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D93" s="28" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E93" s="41"/>
       <c r="F93" s="28" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="G93" s="28" t="s">
         <v>23</v>
       </c>
       <c r="H93" s="43" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I93" s="28" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J93" s="28" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="K93" s="44">
         <f t="shared" si="6"/>
@@ -18159,7 +18279,7 @@
         <v>27</v>
       </c>
       <c r="O93" s="21" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="P93" s="20" t="s">
         <v>29</v>
@@ -18174,26 +18294,26 @@
         <v>73</v>
       </c>
       <c r="C94" s="28" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D94" s="28" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E94" s="41"/>
       <c r="F94" s="28" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="G94" s="28" t="s">
         <v>23</v>
       </c>
       <c r="H94" s="43" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I94" s="28" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J94" s="28" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="K94" s="44">
         <f t="shared" si="6"/>
@@ -18209,7 +18329,7 @@
         <v>27</v>
       </c>
       <c r="O94" s="21" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="P94" s="20" t="s">
         <v>29</v>
@@ -18224,26 +18344,26 @@
         <v>74</v>
       </c>
       <c r="C95" s="28" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D95" s="28" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E95" s="41"/>
       <c r="F95" s="28" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="G95" s="28" t="s">
         <v>23</v>
       </c>
       <c r="H95" s="43" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I95" s="28" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J95" s="28" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="K95" s="44">
         <f t="shared" si="6"/>
@@ -18259,7 +18379,7 @@
         <v>27</v>
       </c>
       <c r="O95" s="21" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="P95" s="20" t="s">
         <v>29</v>
@@ -18274,26 +18394,26 @@
         <v>75</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D96" s="11" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E96" s="12"/>
       <c r="F96" s="11" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="G96" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H96" s="22" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I96" s="11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J96" s="11" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="K96" s="46">
         <f t="shared" si="6"/>
@@ -18309,7 +18429,7 @@
         <v>27</v>
       </c>
       <c r="O96" s="21" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="P96" s="20" t="s">
         <v>29</v>
@@ -18320,26 +18440,26 @@
         <v>76</v>
       </c>
       <c r="C97" s="28" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D97" s="28" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E97" s="41"/>
       <c r="F97" s="28" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="G97" s="28" t="s">
         <v>23</v>
       </c>
       <c r="H97" s="43" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I97" s="28" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J97" s="28" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="K97" s="44">
         <f t="shared" si="6"/>
@@ -18355,7 +18475,7 @@
         <v>27</v>
       </c>
       <c r="O97" s="21" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="P97" s="20" t="s">
         <v>29</v>
@@ -18370,26 +18490,26 @@
         <v>77</v>
       </c>
       <c r="C98" s="28" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D98" s="28" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E98" s="41"/>
       <c r="F98" s="28" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="G98" s="28" t="s">
         <v>23</v>
       </c>
       <c r="H98" s="43" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I98" s="28" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J98" s="28" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="K98" s="44">
         <f t="shared" si="6"/>
@@ -18405,7 +18525,7 @@
         <v>27</v>
       </c>
       <c r="O98" s="21" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="P98" s="20" t="s">
         <v>29</v>
@@ -18420,26 +18540,26 @@
         <v>78</v>
       </c>
       <c r="C99" s="28" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="D99" s="28" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E99" s="41"/>
       <c r="F99" s="28" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="G99" s="28" t="s">
         <v>23</v>
       </c>
       <c r="H99" s="43" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I99" s="28" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J99" s="28" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="K99" s="44">
         <f t="shared" si="6"/>
@@ -18455,7 +18575,7 @@
         <v>27</v>
       </c>
       <c r="O99" s="21" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="P99" s="20" t="s">
         <v>29</v>
@@ -18470,26 +18590,26 @@
         <v>79</v>
       </c>
       <c r="C100" s="28" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="D100" s="28" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E100" s="41"/>
       <c r="F100" s="28" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="G100" s="28" t="s">
         <v>23</v>
       </c>
       <c r="H100" s="43" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I100" s="28" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J100" s="28" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="K100" s="44">
         <f t="shared" si="6"/>
@@ -18505,7 +18625,7 @@
         <v>27</v>
       </c>
       <c r="O100" s="21" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="P100" s="20" t="s">
         <v>29</v>
@@ -18520,26 +18640,26 @@
         <v>80</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="D101" s="11" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E101" s="12"/>
       <c r="F101" s="11" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="G101" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H101" s="22" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I101" s="11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J101" s="11" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="K101" s="46">
         <f t="shared" si="6"/>
@@ -18555,7 +18675,7 @@
         <v>27</v>
       </c>
       <c r="O101" s="21" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="P101" s="20" t="s">
         <v>29</v>
@@ -18566,26 +18686,26 @@
         <v>81</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D102" s="11" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E102" s="12"/>
       <c r="F102" s="11" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G102" s="11" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="H102" s="22" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I102" s="11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J102" s="11" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="K102" s="46">
         <f t="shared" si="6"/>
@@ -18601,7 +18721,7 @@
         <v>27</v>
       </c>
       <c r="O102" s="21" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="P102" s="20" t="s">
         <v>29</v>
@@ -18612,26 +18732,26 @@
         <v>82</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="D103" s="11" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E103" s="12"/>
       <c r="F103" s="11" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="G103" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H103" s="22" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I103" s="11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J103" s="11" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="K103" s="46">
         <f t="shared" si="6"/>
@@ -18647,7 +18767,7 @@
         <v>27</v>
       </c>
       <c r="O103" s="21" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="P103" s="20" t="s">
         <v>29</v>
@@ -18658,26 +18778,26 @@
         <v>83</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="D104" s="11" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E104" s="12"/>
       <c r="F104" s="11" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="G104" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H104" s="22" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I104" s="11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J104" s="11" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="K104" s="46">
         <f t="shared" si="6"/>
@@ -18693,7 +18813,7 @@
         <v>27</v>
       </c>
       <c r="O104" s="21" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="P104" s="20" t="s">
         <v>29</v>
@@ -18704,26 +18824,26 @@
         <v>84</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="D105" s="11" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E105" s="12"/>
       <c r="F105" s="11" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="G105" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H105" s="22" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I105" s="11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J105" s="11" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="K105" s="46">
         <f t="shared" si="6"/>
@@ -18739,7 +18859,7 @@
         <v>27</v>
       </c>
       <c r="O105" s="21" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="P105" s="20" t="s">
         <v>29</v>
@@ -18750,26 +18870,26 @@
         <v>85</v>
       </c>
       <c r="C106" s="28" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D106" s="28" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E106" s="41"/>
       <c r="F106" s="28" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="G106" s="28" t="s">
         <v>23</v>
       </c>
       <c r="H106" s="43" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I106" s="28" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J106" s="28" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="K106" s="44">
         <f t="shared" si="6"/>
@@ -18785,7 +18905,7 @@
         <v>27</v>
       </c>
       <c r="O106" s="21" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="P106" s="20" t="s">
         <v>29</v>
@@ -18800,26 +18920,26 @@
         <v>86</v>
       </c>
       <c r="C107" s="28" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="D107" s="28" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E107" s="41"/>
       <c r="F107" s="28" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="G107" s="28" t="s">
         <v>23</v>
       </c>
       <c r="H107" s="43" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I107" s="28" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J107" s="28" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="K107" s="44">
         <f t="shared" si="6"/>
@@ -18835,7 +18955,7 @@
         <v>27</v>
       </c>
       <c r="O107" s="21" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="P107" s="20" t="s">
         <v>29</v>
@@ -18850,26 +18970,26 @@
         <v>87</v>
       </c>
       <c r="C108" s="28" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="D108" s="28" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E108" s="41"/>
       <c r="F108" s="28" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="G108" s="28" t="s">
         <v>23</v>
       </c>
       <c r="H108" s="43" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I108" s="28" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J108" s="28" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="K108" s="44">
         <f t="shared" si="6"/>
@@ -18885,7 +19005,7 @@
         <v>27</v>
       </c>
       <c r="O108" s="21" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="P108" s="20" t="s">
         <v>29</v>
@@ -18900,23 +19020,23 @@
         <v>88</v>
       </c>
       <c r="C109" s="11" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D109" s="11" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E109" s="12"/>
       <c r="F109" s="11" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="G109" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H109" s="22" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I109" s="11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J109" s="11" t="s">
         <v>42</v>
@@ -18935,7 +19055,7 @@
         <v>27</v>
       </c>
       <c r="O109" s="21" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="P109" s="20" t="s">
         <v>29</v>
@@ -18946,23 +19066,23 @@
         <v>89</v>
       </c>
       <c r="C110" s="11" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D110" s="11" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E110" s="12"/>
       <c r="F110" s="11" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="G110" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H110" s="22" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I110" s="11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J110" s="11" t="s">
         <v>42</v>
@@ -18981,7 +19101,7 @@
         <v>27</v>
       </c>
       <c r="O110" s="21" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="P110" s="20" t="s">
         <v>29</v>
@@ -18992,23 +19112,23 @@
         <v>90</v>
       </c>
       <c r="C111" s="11" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="D111" s="11" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E111" s="12"/>
       <c r="F111" s="11" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="G111" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H111" s="22" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I111" s="11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J111" s="11" t="s">
         <v>42</v>
@@ -19027,32 +19147,32 @@
         <v>27</v>
       </c>
       <c r="O111" s="21" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="P111" s="20" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="112" spans="2:20" ht="50.1" customHeight="1">
-      <c r="B112" s="63" t="s">
-        <v>359</v>
-      </c>
-      <c r="C112" s="64"/>
-      <c r="D112" s="64"/>
-      <c r="E112" s="64"/>
-      <c r="F112" s="64"/>
-      <c r="G112" s="64"/>
-      <c r="H112" s="64"/>
-      <c r="I112" s="64"/>
-      <c r="J112" s="64"/>
-      <c r="K112" s="64"/>
-      <c r="L112" s="64"/>
-      <c r="M112" s="65"/>
+      <c r="B112" s="90" t="s">
+        <v>356</v>
+      </c>
+      <c r="C112" s="91"/>
+      <c r="D112" s="91"/>
+      <c r="E112" s="91"/>
+      <c r="F112" s="91"/>
+      <c r="G112" s="91"/>
+      <c r="H112" s="91"/>
+      <c r="I112" s="91"/>
+      <c r="J112" s="91"/>
+      <c r="K112" s="91"/>
+      <c r="L112" s="91"/>
+      <c r="M112" s="92"/>
       <c r="N112" s="19" t="s">
         <v>27</v>
       </c>
       <c r="O112" s="21" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="P112" s="20" t="s">
         <v>29</v>
@@ -19063,26 +19183,26 @@
         <v>91</v>
       </c>
       <c r="C113" s="11" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="D113" s="11" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="E113" s="12"/>
       <c r="F113" s="48" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="G113" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H113" s="22" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I113" s="11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J113" s="11" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K113" s="46">
         <f t="shared" ref="K113:K130" si="7">L113*(1-22%)</f>
@@ -19098,7 +19218,7 @@
         <v>27</v>
       </c>
       <c r="O113" s="21" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="P113" s="20" t="s">
         <v>29</v>
@@ -19109,26 +19229,26 @@
         <v>92</v>
       </c>
       <c r="C114" s="11" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="D114" s="11" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="E114" s="12"/>
       <c r="F114" s="48" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G114" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H114" s="22" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I114" s="11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J114" s="11" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K114" s="46">
         <f t="shared" si="7"/>
@@ -19144,7 +19264,7 @@
         <v>27</v>
       </c>
       <c r="O114" s="21" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="P114" s="20" t="s">
         <v>29</v>
@@ -19155,26 +19275,26 @@
         <v>93</v>
       </c>
       <c r="C115" s="11" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="D115" s="11" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="E115" s="12"/>
       <c r="F115" s="48" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="G115" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H115" s="22" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I115" s="11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J115" s="11" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K115" s="46">
         <f t="shared" si="7"/>
@@ -19190,7 +19310,7 @@
         <v>27</v>
       </c>
       <c r="O115" s="21" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="P115" s="20" t="s">
         <v>29</v>
@@ -19201,26 +19321,26 @@
         <v>94</v>
       </c>
       <c r="C116" s="11" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="D116" s="11" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="E116" s="12"/>
       <c r="F116" s="48" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="G116" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H116" s="22" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I116" s="11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J116" s="11" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K116" s="46">
         <f t="shared" si="7"/>
@@ -19236,7 +19356,7 @@
         <v>27</v>
       </c>
       <c r="O116" s="21" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="P116" s="20" t="s">
         <v>29</v>
@@ -19247,26 +19367,26 @@
         <v>95</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D117" s="11" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="E117" s="12"/>
       <c r="F117" s="48" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="G117" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H117" s="22" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I117" s="11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J117" s="11" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K117" s="46">
         <f t="shared" si="7"/>
@@ -19282,7 +19402,7 @@
         <v>27</v>
       </c>
       <c r="O117" s="21" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="P117" s="20" t="s">
         <v>29</v>
@@ -19293,26 +19413,26 @@
         <v>96</v>
       </c>
       <c r="C118" s="11" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D118" s="11" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="E118" s="12"/>
       <c r="F118" s="48" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="G118" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H118" s="22" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I118" s="11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J118" s="11" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K118" s="46">
         <f t="shared" si="7"/>
@@ -19328,7 +19448,7 @@
         <v>27</v>
       </c>
       <c r="O118" s="21" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="P118" s="20" t="s">
         <v>29</v>
@@ -19339,26 +19459,26 @@
         <v>97</v>
       </c>
       <c r="C119" s="28" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="D119" s="28" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="E119" s="41"/>
       <c r="F119" s="49" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="G119" s="28" t="s">
         <v>23</v>
       </c>
       <c r="H119" s="43" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I119" s="28" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J119" s="28" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K119" s="44">
         <f t="shared" si="7"/>
@@ -19374,7 +19494,7 @@
         <v>27</v>
       </c>
       <c r="O119" s="21" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="P119" s="20" t="s">
         <v>29</v>
@@ -19389,26 +19509,26 @@
         <v>98</v>
       </c>
       <c r="C120" s="28" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D120" s="28" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="E120" s="41"/>
       <c r="F120" s="49" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="G120" s="28" t="s">
         <v>23</v>
       </c>
       <c r="H120" s="43" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I120" s="28" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J120" s="28" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K120" s="44">
         <f t="shared" si="7"/>
@@ -19424,7 +19544,7 @@
         <v>27</v>
       </c>
       <c r="O120" s="21" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="P120" s="20" t="s">
         <v>29</v>
@@ -19439,26 +19559,26 @@
         <v>99</v>
       </c>
       <c r="C121" s="28" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D121" s="28" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="E121" s="41"/>
       <c r="F121" s="49" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="G121" s="28" t="s">
         <v>23</v>
       </c>
       <c r="H121" s="43" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I121" s="28" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J121" s="28" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K121" s="44">
         <f t="shared" si="7"/>
@@ -19474,7 +19594,7 @@
         <v>27</v>
       </c>
       <c r="O121" s="21" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="P121" s="20" t="s">
         <v>29</v>
@@ -19489,26 +19609,26 @@
         <v>100</v>
       </c>
       <c r="C122" s="28" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="D122" s="28" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="E122" s="41"/>
       <c r="F122" s="49" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G122" s="28" t="s">
         <v>23</v>
       </c>
       <c r="H122" s="43" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I122" s="28" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J122" s="28" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K122" s="44">
         <f t="shared" si="7"/>
@@ -19524,7 +19644,7 @@
         <v>27</v>
       </c>
       <c r="O122" s="21" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="P122" s="20" t="s">
         <v>29</v>
@@ -19539,26 +19659,26 @@
         <v>101</v>
       </c>
       <c r="C123" s="11" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="D123" s="11" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="E123" s="12"/>
       <c r="F123" s="48" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="G123" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H123" s="22" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I123" s="11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J123" s="11" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K123" s="46">
         <f t="shared" si="7"/>
@@ -19574,7 +19694,7 @@
         <v>27</v>
       </c>
       <c r="O123" s="21" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="P123" s="20" t="s">
         <v>29</v>
@@ -19585,26 +19705,26 @@
         <v>102</v>
       </c>
       <c r="C124" s="28" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="D124" s="28" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="E124" s="41"/>
       <c r="F124" s="49" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="G124" s="28" t="s">
         <v>23</v>
       </c>
       <c r="H124" s="43" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I124" s="28" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J124" s="28" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K124" s="44">
         <f t="shared" si="7"/>
@@ -19620,7 +19740,7 @@
         <v>27</v>
       </c>
       <c r="O124" s="21" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="P124" s="20" t="s">
         <v>29</v>
@@ -19635,26 +19755,26 @@
         <v>103</v>
       </c>
       <c r="C125" s="28" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="D125" s="28" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="E125" s="41"/>
       <c r="F125" s="49" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="G125" s="28" t="s">
         <v>23</v>
       </c>
       <c r="H125" s="43" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I125" s="28" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J125" s="28" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K125" s="44">
         <f t="shared" si="7"/>
@@ -19670,7 +19790,7 @@
         <v>27</v>
       </c>
       <c r="O125" s="21" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="P125" s="20" t="s">
         <v>29</v>
@@ -19685,26 +19805,26 @@
         <v>104</v>
       </c>
       <c r="C126" s="28" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="D126" s="28" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="E126" s="41"/>
       <c r="F126" s="49" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="G126" s="28" t="s">
         <v>23</v>
       </c>
       <c r="H126" s="43" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I126" s="28" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J126" s="28" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K126" s="44">
         <f t="shared" si="7"/>
@@ -19720,7 +19840,7 @@
         <v>27</v>
       </c>
       <c r="O126" s="21" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="P126" s="20" t="s">
         <v>29</v>
@@ -19735,26 +19855,26 @@
         <v>105</v>
       </c>
       <c r="C127" s="11" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="D127" s="11" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="E127" s="12"/>
       <c r="F127" s="48" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="G127" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H127" s="22" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I127" s="11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J127" s="11" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K127" s="46">
         <f t="shared" si="7"/>
@@ -19770,7 +19890,7 @@
         <v>27</v>
       </c>
       <c r="O127" s="21" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="P127" s="20" t="s">
         <v>29</v>
@@ -19781,26 +19901,26 @@
         <v>106</v>
       </c>
       <c r="C128" s="11" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="D128" s="11" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="E128" s="12"/>
       <c r="F128" s="48" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="G128" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H128" s="22" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I128" s="11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J128" s="11" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K128" s="46">
         <f t="shared" si="7"/>
@@ -19816,7 +19936,7 @@
         <v>27</v>
       </c>
       <c r="O128" s="21" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="P128" s="20" t="s">
         <v>29</v>
@@ -19827,26 +19947,26 @@
         <v>107</v>
       </c>
       <c r="C129" s="11" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="D129" s="11" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="E129" s="12"/>
       <c r="F129" s="48" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="G129" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H129" s="22" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I129" s="11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J129" s="11" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K129" s="46">
         <f t="shared" si="7"/>
@@ -19862,7 +19982,7 @@
         <v>27</v>
       </c>
       <c r="O129" s="21" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="P129" s="20" t="s">
         <v>29</v>
@@ -19873,26 +19993,26 @@
         <v>108</v>
       </c>
       <c r="C130" s="28" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="D130" s="28" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="E130" s="41"/>
       <c r="F130" s="49" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="G130" s="28" t="s">
         <v>23</v>
       </c>
       <c r="H130" s="43" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I130" s="28" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J130" s="28" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K130" s="44">
         <f t="shared" si="7"/>
@@ -19908,7 +20028,7 @@
         <v>27</v>
       </c>
       <c r="O130" s="21" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="P130" s="20" t="s">
         <v>29</v>
@@ -19919,25 +20039,25 @@
       <c r="T130" s="32"/>
     </row>
     <row r="131" spans="2:20" ht="50.1" customHeight="1">
-      <c r="B131" s="63" t="s">
-        <v>414</v>
-      </c>
-      <c r="C131" s="64"/>
-      <c r="D131" s="64"/>
-      <c r="E131" s="64"/>
-      <c r="F131" s="64"/>
-      <c r="G131" s="64"/>
-      <c r="H131" s="64"/>
-      <c r="I131" s="64"/>
-      <c r="J131" s="64"/>
-      <c r="K131" s="64"/>
-      <c r="L131" s="64"/>
-      <c r="M131" s="65"/>
+      <c r="B131" s="90" t="s">
+        <v>411</v>
+      </c>
+      <c r="C131" s="91"/>
+      <c r="D131" s="91"/>
+      <c r="E131" s="91"/>
+      <c r="F131" s="91"/>
+      <c r="G131" s="91"/>
+      <c r="H131" s="91"/>
+      <c r="I131" s="91"/>
+      <c r="J131" s="91"/>
+      <c r="K131" s="91"/>
+      <c r="L131" s="91"/>
+      <c r="M131" s="92"/>
       <c r="N131" s="19" t="s">
         <v>27</v>
       </c>
       <c r="O131" s="21" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="P131" s="20" t="s">
         <v>29</v>
@@ -19948,26 +20068,26 @@
         <v>109</v>
       </c>
       <c r="C132" s="11" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="D132" s="11" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="E132" s="12"/>
       <c r="F132" s="11" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="G132" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H132" s="22" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I132" s="11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J132" s="11" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K132" s="46">
         <f t="shared" ref="K132:K148" si="8">L132*(1-22%)</f>
@@ -19983,7 +20103,7 @@
         <v>27</v>
       </c>
       <c r="O132" s="21" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="P132" s="20" t="s">
         <v>29</v>
@@ -19994,26 +20114,26 @@
         <v>110</v>
       </c>
       <c r="C133" s="11" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D133" s="11" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="E133" s="12"/>
       <c r="F133" s="11" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="G133" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H133" s="22" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I133" s="11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J133" s="11" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K133" s="46">
         <f t="shared" si="8"/>
@@ -20029,7 +20149,7 @@
         <v>27</v>
       </c>
       <c r="O133" s="21" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="P133" s="20" t="s">
         <v>29</v>
@@ -20040,26 +20160,26 @@
         <v>111</v>
       </c>
       <c r="C134" s="11" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="D134" s="11" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="E134" s="12"/>
       <c r="F134" s="11" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="G134" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H134" s="22" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I134" s="11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J134" s="11" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K134" s="46">
         <f t="shared" si="8"/>
@@ -20075,7 +20195,7 @@
         <v>27</v>
       </c>
       <c r="O134" s="21" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="P134" s="20" t="s">
         <v>29</v>
@@ -20086,26 +20206,26 @@
         <v>112</v>
       </c>
       <c r="C135" s="11" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="D135" s="11" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="E135" s="12"/>
       <c r="F135" s="11" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="G135" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H135" s="22" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I135" s="11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J135" s="11" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K135" s="46">
         <f t="shared" si="8"/>
@@ -20121,7 +20241,7 @@
         <v>27</v>
       </c>
       <c r="O135" s="21" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="P135" s="20" t="s">
         <v>29</v>
@@ -20132,26 +20252,26 @@
         <v>113</v>
       </c>
       <c r="C136" s="11" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="D136" s="11" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="E136" s="12"/>
       <c r="F136" s="11" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="G136" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H136" s="22" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I136" s="11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J136" s="11" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K136" s="46">
         <f t="shared" si="8"/>
@@ -20167,7 +20287,7 @@
         <v>27</v>
       </c>
       <c r="O136" s="21" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="P136" s="20" t="s">
         <v>29</v>
@@ -20178,26 +20298,26 @@
         <v>114</v>
       </c>
       <c r="C137" s="11" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="D137" s="11" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="E137" s="12"/>
       <c r="F137" s="11" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="G137" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H137" s="22" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I137" s="11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J137" s="11" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K137" s="46">
         <f t="shared" si="8"/>
@@ -20213,7 +20333,7 @@
         <v>27</v>
       </c>
       <c r="O137" s="21" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="P137" s="20" t="s">
         <v>29</v>
@@ -20224,26 +20344,26 @@
         <v>115</v>
       </c>
       <c r="C138" s="11" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="D138" s="11" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="E138" s="12"/>
       <c r="F138" s="11" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="G138" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H138" s="22" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I138" s="11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J138" s="11" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K138" s="46">
         <f t="shared" si="8"/>
@@ -20259,7 +20379,7 @@
         <v>27</v>
       </c>
       <c r="O138" s="21" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="P138" s="20" t="s">
         <v>29</v>
@@ -20270,26 +20390,26 @@
         <v>116</v>
       </c>
       <c r="C139" s="11" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="D139" s="11" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="E139" s="12"/>
       <c r="F139" s="11" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="G139" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H139" s="22" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I139" s="11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J139" s="11" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K139" s="46">
         <f t="shared" si="8"/>
@@ -20305,7 +20425,7 @@
         <v>27</v>
       </c>
       <c r="O139" s="21" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="P139" s="20" t="s">
         <v>29</v>
@@ -20316,26 +20436,26 @@
         <v>117</v>
       </c>
       <c r="C140" s="11" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="D140" s="11" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="E140" s="12"/>
       <c r="F140" s="11" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="G140" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H140" s="22" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I140" s="11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J140" s="11" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K140" s="46">
         <f t="shared" si="8"/>
@@ -20351,7 +20471,7 @@
         <v>27</v>
       </c>
       <c r="O140" s="21" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="P140" s="20" t="s">
         <v>29</v>
@@ -20362,26 +20482,26 @@
         <v>118</v>
       </c>
       <c r="C141" s="11" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D141" s="11" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="E141" s="12"/>
       <c r="F141" s="11" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="G141" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H141" s="22" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I141" s="11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J141" s="11" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K141" s="46">
         <f t="shared" si="8"/>
@@ -20397,7 +20517,7 @@
         <v>27</v>
       </c>
       <c r="O141" s="21" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="P141" s="20" t="s">
         <v>29</v>
@@ -20408,26 +20528,26 @@
         <v>119</v>
       </c>
       <c r="C142" s="11" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="D142" s="11" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="E142" s="12"/>
       <c r="F142" s="11" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="G142" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H142" s="22" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I142" s="11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J142" s="11" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K142" s="46">
         <f t="shared" si="8"/>
@@ -20443,7 +20563,7 @@
         <v>27</v>
       </c>
       <c r="O142" s="21" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="P142" s="20" t="s">
         <v>29</v>
@@ -20454,26 +20574,26 @@
         <v>120</v>
       </c>
       <c r="C143" s="11" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="D143" s="11" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="E143" s="12"/>
       <c r="F143" s="11" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="G143" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H143" s="22" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I143" s="11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J143" s="11" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="K143" s="46">
         <f t="shared" si="8"/>
@@ -20489,7 +20609,7 @@
         <v>27</v>
       </c>
       <c r="O143" s="21" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="P143" s="20" t="s">
         <v>29</v>
@@ -20500,26 +20620,26 @@
         <v>121</v>
       </c>
       <c r="C144" s="11" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="D144" s="11" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="E144" s="12"/>
       <c r="F144" s="11" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="G144" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H144" s="22" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I144" s="11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J144" s="11" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K144" s="46">
         <f t="shared" si="8"/>
@@ -20535,7 +20655,7 @@
         <v>27</v>
       </c>
       <c r="O144" s="21" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="P144" s="20" t="s">
         <v>29</v>
@@ -20546,26 +20666,26 @@
         <v>122</v>
       </c>
       <c r="C145" s="28" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="D145" s="28" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="E145" s="41"/>
       <c r="F145" s="28" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="G145" s="28" t="s">
         <v>23</v>
       </c>
       <c r="H145" s="43" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I145" s="28" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J145" s="28" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="K145" s="44">
         <f t="shared" si="8"/>
@@ -20581,7 +20701,7 @@
         <v>27</v>
       </c>
       <c r="O145" s="21" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="P145" s="20" t="s">
         <v>29</v>
@@ -20596,26 +20716,26 @@
         <v>123</v>
       </c>
       <c r="C146" s="11" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="D146" s="11" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="E146" s="12"/>
       <c r="F146" s="11" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="G146" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H146" s="22" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I146" s="11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J146" s="11" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K146" s="46">
         <f t="shared" si="8"/>
@@ -20631,7 +20751,7 @@
         <v>27</v>
       </c>
       <c r="O146" s="21" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="P146" s="20" t="s">
         <v>29</v>
@@ -20642,26 +20762,26 @@
         <v>124</v>
       </c>
       <c r="C147" s="11" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="D147" s="11" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="E147" s="12"/>
       <c r="F147" s="11" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="G147" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H147" s="22" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I147" s="11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J147" s="11" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K147" s="46">
         <f t="shared" si="8"/>
@@ -20677,7 +20797,7 @@
         <v>27</v>
       </c>
       <c r="O147" s="21" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="P147" s="20" t="s">
         <v>29</v>
@@ -20688,26 +20808,26 @@
         <v>125</v>
       </c>
       <c r="C148" s="11" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="D148" s="11" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="E148" s="12"/>
       <c r="F148" s="11" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="G148" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H148" s="22" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="I148" s="11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J148" s="11" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K148" s="46">
         <f t="shared" si="8"/>
@@ -20723,32 +20843,32 @@
         <v>27</v>
       </c>
       <c r="O148" s="21" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="P148" s="20" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="149" spans="2:20" ht="50.1" customHeight="1">
-      <c r="B149" s="63" t="s">
-        <v>461</v>
-      </c>
-      <c r="C149" s="64"/>
-      <c r="D149" s="64"/>
-      <c r="E149" s="64"/>
-      <c r="F149" s="64"/>
-      <c r="G149" s="64"/>
-      <c r="H149" s="64"/>
-      <c r="I149" s="64"/>
-      <c r="J149" s="64"/>
-      <c r="K149" s="64"/>
-      <c r="L149" s="64"/>
-      <c r="M149" s="65"/>
+      <c r="B149" s="90" t="s">
+        <v>458</v>
+      </c>
+      <c r="C149" s="91"/>
+      <c r="D149" s="91"/>
+      <c r="E149" s="91"/>
+      <c r="F149" s="91"/>
+      <c r="G149" s="91"/>
+      <c r="H149" s="91"/>
+      <c r="I149" s="91"/>
+      <c r="J149" s="91"/>
+      <c r="K149" s="91"/>
+      <c r="L149" s="91"/>
+      <c r="M149" s="92"/>
       <c r="N149" s="19" t="s">
         <v>27</v>
       </c>
       <c r="O149" s="21" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="P149" s="20" t="s">
         <v>29</v>
@@ -20759,26 +20879,26 @@
         <v>126</v>
       </c>
       <c r="C150" s="28" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="D150" s="28" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="E150" s="41"/>
       <c r="F150" s="28" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G150" s="28" t="s">
         <v>23</v>
       </c>
       <c r="H150" s="50" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="I150" s="28" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J150" s="28" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K150" s="40">
         <f>L150*(1-0.22)</f>
@@ -20792,7 +20912,7 @@
         <v>27</v>
       </c>
       <c r="O150" s="21" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="P150" s="20" t="s">
         <v>29</v>
@@ -20807,26 +20927,26 @@
         <v>127</v>
       </c>
       <c r="C151" s="28" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="D151" s="28" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="E151" s="41"/>
       <c r="F151" s="28" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G151" s="28" t="s">
         <v>23</v>
       </c>
       <c r="H151" s="50" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="I151" s="28" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J151" s="28" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="K151" s="40">
         <f>L151*(1-0.22)</f>
@@ -20840,7 +20960,7 @@
         <v>27</v>
       </c>
       <c r="O151" s="21" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="P151" s="20" t="s">
         <v>29</v>
@@ -20855,26 +20975,26 @@
         <v>128</v>
       </c>
       <c r="C152" s="11" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D152" s="11" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="E152" s="12"/>
       <c r="F152" s="11" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="G152" s="11" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H152" s="51" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="I152" s="11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J152" s="11" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="K152" s="16">
         <f>L152*(1-0.22)</f>
@@ -20890,7 +21010,7 @@
         <v>27</v>
       </c>
       <c r="O152" s="21" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="P152" s="20" t="s">
         <v>29</v>
@@ -20901,26 +21021,26 @@
         <v>129</v>
       </c>
       <c r="C153" s="11" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D153" s="11" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="E153" s="12"/>
       <c r="F153" s="11" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G153" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H153" s="51" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="I153" s="11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J153" s="11" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="K153" s="16">
         <f>L153*(1-0.22)</f>
@@ -20936,7 +21056,7 @@
         <v>27</v>
       </c>
       <c r="O153" s="21" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="P153" s="20" t="s">
         <v>29</v>
@@ -20947,26 +21067,26 @@
         <v>130</v>
       </c>
       <c r="C154" s="11" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="D154" s="11" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="E154" s="12"/>
       <c r="F154" s="11" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="G154" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H154" s="22" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="I154" s="11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J154" s="11" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="K154" s="16">
         <f>L154*(1-0.22)</f>
@@ -20982,32 +21102,32 @@
         <v>27</v>
       </c>
       <c r="O154" s="21" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="P154" s="20" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="155" spans="2:20" ht="50.1" customHeight="1">
-      <c r="B155" s="63" t="s">
-        <v>484</v>
-      </c>
-      <c r="C155" s="64"/>
-      <c r="D155" s="64"/>
-      <c r="E155" s="64"/>
-      <c r="F155" s="64"/>
-      <c r="G155" s="64"/>
-      <c r="H155" s="64"/>
-      <c r="I155" s="64"/>
-      <c r="J155" s="64"/>
-      <c r="K155" s="64"/>
-      <c r="L155" s="64"/>
-      <c r="M155" s="65"/>
+      <c r="B155" s="90" t="s">
+        <v>481</v>
+      </c>
+      <c r="C155" s="91"/>
+      <c r="D155" s="91"/>
+      <c r="E155" s="91"/>
+      <c r="F155" s="91"/>
+      <c r="G155" s="91"/>
+      <c r="H155" s="91"/>
+      <c r="I155" s="91"/>
+      <c r="J155" s="91"/>
+      <c r="K155" s="91"/>
+      <c r="L155" s="91"/>
+      <c r="M155" s="92"/>
       <c r="N155" s="19" t="s">
         <v>27</v>
       </c>
       <c r="O155" s="21" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="P155" s="20" t="s">
         <v>29</v>
@@ -21018,26 +21138,26 @@
         <v>131</v>
       </c>
       <c r="C156" s="28" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="D156" s="28" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="E156" s="41"/>
       <c r="F156" s="28" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="G156" s="28" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H156" s="43" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="I156" s="28" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J156" s="28" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K156" s="40">
         <f>L156*(1-0.22)</f>
@@ -21053,7 +21173,7 @@
         <v>27</v>
       </c>
       <c r="O156" s="21" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="P156" s="20" t="s">
         <v>29</v>
@@ -21064,25 +21184,25 @@
       <c r="T156" s="32"/>
     </row>
     <row r="157" spans="2:20" ht="50.1" customHeight="1">
-      <c r="B157" s="63" t="s">
-        <v>490</v>
-      </c>
-      <c r="C157" s="64"/>
-      <c r="D157" s="64"/>
-      <c r="E157" s="64"/>
-      <c r="F157" s="64"/>
-      <c r="G157" s="64"/>
-      <c r="H157" s="64"/>
-      <c r="I157" s="64"/>
-      <c r="J157" s="64"/>
-      <c r="K157" s="64"/>
-      <c r="L157" s="64"/>
-      <c r="M157" s="65"/>
+      <c r="B157" s="90" t="s">
+        <v>487</v>
+      </c>
+      <c r="C157" s="91"/>
+      <c r="D157" s="91"/>
+      <c r="E157" s="91"/>
+      <c r="F157" s="91"/>
+      <c r="G157" s="91"/>
+      <c r="H157" s="91"/>
+      <c r="I157" s="91"/>
+      <c r="J157" s="91"/>
+      <c r="K157" s="91"/>
+      <c r="L157" s="91"/>
+      <c r="M157" s="92"/>
       <c r="N157" s="19" t="s">
         <v>27</v>
       </c>
       <c r="O157" s="21" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="P157" s="20" t="s">
         <v>29</v>
@@ -21093,26 +21213,26 @@
         <v>132</v>
       </c>
       <c r="C158" s="28" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="D158" s="28" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="E158" s="41"/>
       <c r="F158" s="28" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="G158" s="28" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H158" s="28" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="I158" s="28" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J158" s="28" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K158" s="40">
         <f>L158*(1-0.22)</f>
@@ -21128,7 +21248,7 @@
         <v>27</v>
       </c>
       <c r="O158" s="21" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="P158" s="20" t="s">
         <v>29</v>
@@ -21139,25 +21259,25 @@
       <c r="T158" s="32"/>
     </row>
     <row r="159" spans="2:20" ht="50.1" customHeight="1">
-      <c r="B159" s="63" t="s">
-        <v>495</v>
-      </c>
-      <c r="C159" s="64"/>
-      <c r="D159" s="64"/>
-      <c r="E159" s="64"/>
-      <c r="F159" s="64"/>
-      <c r="G159" s="64"/>
-      <c r="H159" s="64"/>
-      <c r="I159" s="64"/>
-      <c r="J159" s="64"/>
-      <c r="K159" s="64"/>
-      <c r="L159" s="64"/>
-      <c r="M159" s="65"/>
+      <c r="B159" s="90" t="s">
+        <v>492</v>
+      </c>
+      <c r="C159" s="91"/>
+      <c r="D159" s="91"/>
+      <c r="E159" s="91"/>
+      <c r="F159" s="91"/>
+      <c r="G159" s="91"/>
+      <c r="H159" s="91"/>
+      <c r="I159" s="91"/>
+      <c r="J159" s="91"/>
+      <c r="K159" s="91"/>
+      <c r="L159" s="91"/>
+      <c r="M159" s="92"/>
       <c r="N159" s="19" t="s">
         <v>27</v>
       </c>
       <c r="O159" s="21" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="P159" s="20" t="s">
         <v>29</v>
@@ -21168,10 +21288,10 @@
         <v>133</v>
       </c>
       <c r="C160" s="11" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="D160" s="11" t="s">
-        <v>498</v>
+        <v>623</v>
       </c>
       <c r="E160" s="12"/>
       <c r="F160" s="16" t="s">
@@ -21181,13 +21301,13 @@
         <v>23</v>
       </c>
       <c r="H160" s="22" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="I160" s="11" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="J160" s="11" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="K160" s="16">
         <f>L160*(1-0.22)</f>
@@ -21203,7 +21323,7 @@
         <v>27</v>
       </c>
       <c r="O160" s="21" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="P160" s="20" t="s">
         <v>29</v>
@@ -21214,10 +21334,10 @@
         <v>134</v>
       </c>
       <c r="C161" s="11" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D161" s="11" t="s">
-        <v>498</v>
+        <v>624</v>
       </c>
       <c r="E161" s="12"/>
       <c r="F161" s="16" t="s">
@@ -21227,13 +21347,13 @@
         <v>23</v>
       </c>
       <c r="H161" s="22" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="I161" s="11" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="J161" s="11" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="K161" s="16">
         <f>L161*(1-0.22)</f>
@@ -21249,32 +21369,32 @@
         <v>27</v>
       </c>
       <c r="O161" s="21" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="P161" s="20" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="162" spans="2:20" ht="50.1" customHeight="1">
-      <c r="B162" s="63" t="s">
-        <v>504</v>
-      </c>
-      <c r="C162" s="64"/>
-      <c r="D162" s="64"/>
-      <c r="E162" s="64"/>
-      <c r="F162" s="64"/>
-      <c r="G162" s="64"/>
-      <c r="H162" s="64"/>
-      <c r="I162" s="64"/>
-      <c r="J162" s="64"/>
-      <c r="K162" s="64"/>
-      <c r="L162" s="64"/>
-      <c r="M162" s="65"/>
+      <c r="B162" s="90" t="s">
+        <v>501</v>
+      </c>
+      <c r="C162" s="91"/>
+      <c r="D162" s="91"/>
+      <c r="E162" s="91"/>
+      <c r="F162" s="91"/>
+      <c r="G162" s="91"/>
+      <c r="H162" s="91"/>
+      <c r="I162" s="91"/>
+      <c r="J162" s="91"/>
+      <c r="K162" s="91"/>
+      <c r="L162" s="91"/>
+      <c r="M162" s="92"/>
       <c r="N162" s="19" t="s">
         <v>27</v>
       </c>
       <c r="O162" s="21" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="P162" s="20" t="s">
         <v>29</v>
@@ -21285,10 +21405,10 @@
         <v>135</v>
       </c>
       <c r="C163" s="28" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="D163" s="28" t="s">
-        <v>504</v>
+        <v>625</v>
       </c>
       <c r="E163" s="41"/>
       <c r="F163" s="40" t="s">
@@ -21298,13 +21418,13 @@
         <v>23</v>
       </c>
       <c r="H163" s="43" t="s">
+        <v>501</v>
+      </c>
+      <c r="I163" s="28" t="s">
         <v>504</v>
       </c>
-      <c r="I163" s="28" t="s">
-        <v>507</v>
-      </c>
       <c r="J163" s="28" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="K163" s="40">
         <f>L163*(1-0.22)</f>
@@ -21320,7 +21440,7 @@
         <v>27</v>
       </c>
       <c r="O163" s="21" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="P163" s="20" t="s">
         <v>29</v>
@@ -21335,10 +21455,10 @@
         <v>136</v>
       </c>
       <c r="C164" s="28" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D164" s="28" t="s">
-        <v>504</v>
+        <v>626</v>
       </c>
       <c r="E164" s="41"/>
       <c r="F164" s="40" t="s">
@@ -21348,13 +21468,13 @@
         <v>23</v>
       </c>
       <c r="H164" s="43" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="I164" s="28" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="J164" s="28" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="K164" s="40">
         <f>L164*(1-0.22)</f>
@@ -21370,7 +21490,7 @@
         <v>27</v>
       </c>
       <c r="O164" s="21" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="P164" s="20" t="s">
         <v>29</v>
@@ -21385,26 +21505,26 @@
         <v>137</v>
       </c>
       <c r="C165" s="28" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D165" s="28" t="s">
-        <v>504</v>
+        <v>627</v>
       </c>
       <c r="E165" s="41"/>
       <c r="F165" s="28" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="G165" s="28" t="s">
         <v>23</v>
       </c>
       <c r="H165" s="43" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="I165" s="28" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="J165" s="28" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="K165" s="40">
         <f>L165*(1-0.22)</f>
@@ -21420,7 +21540,7 @@
         <v>27</v>
       </c>
       <c r="O165" s="21" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="P165" s="20" t="s">
         <v>29</v>
@@ -21435,26 +21555,26 @@
         <v>138</v>
       </c>
       <c r="C166" s="28" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D166" s="28" t="s">
-        <v>504</v>
+        <v>628</v>
       </c>
       <c r="E166" s="41"/>
       <c r="F166" s="28" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="G166" s="28" t="s">
         <v>23</v>
       </c>
       <c r="H166" s="43" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="I166" s="28" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="J166" s="28" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="K166" s="40">
         <f>L166*(1-0.22)</f>
@@ -21470,7 +21590,7 @@
         <v>27</v>
       </c>
       <c r="O166" s="21" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="P166" s="20" t="s">
         <v>29</v>
@@ -21481,25 +21601,25 @@
       <c r="T166" s="32"/>
     </row>
     <row r="167" spans="2:20" ht="50.1" customHeight="1">
-      <c r="B167" s="63" t="s">
-        <v>521</v>
-      </c>
-      <c r="C167" s="64"/>
-      <c r="D167" s="64"/>
-      <c r="E167" s="64"/>
-      <c r="F167" s="64"/>
-      <c r="G167" s="64"/>
-      <c r="H167" s="64"/>
-      <c r="I167" s="64"/>
-      <c r="J167" s="64"/>
-      <c r="K167" s="64"/>
-      <c r="L167" s="64"/>
-      <c r="M167" s="65"/>
+      <c r="B167" s="90" t="s">
+        <v>518</v>
+      </c>
+      <c r="C167" s="91"/>
+      <c r="D167" s="91"/>
+      <c r="E167" s="91"/>
+      <c r="F167" s="91"/>
+      <c r="G167" s="91"/>
+      <c r="H167" s="91"/>
+      <c r="I167" s="91"/>
+      <c r="J167" s="91"/>
+      <c r="K167" s="91"/>
+      <c r="L167" s="91"/>
+      <c r="M167" s="92"/>
       <c r="N167" s="19" t="s">
         <v>27</v>
       </c>
       <c r="O167" s="21" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="P167" s="20" t="s">
         <v>29</v>
@@ -21510,10 +21630,10 @@
         <v>139</v>
       </c>
       <c r="C168" s="11" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="D168" s="11" t="s">
-        <v>524</v>
+        <v>629</v>
       </c>
       <c r="E168" s="12"/>
       <c r="F168" s="16" t="s">
@@ -21523,13 +21643,13 @@
         <v>23</v>
       </c>
       <c r="H168" s="22" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="I168" s="11" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="J168" s="11" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="K168" s="16">
         <f>L168*(1-0.22)</f>
@@ -21545,7 +21665,7 @@
         <v>27</v>
       </c>
       <c r="O168" s="21" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="P168" s="20" t="s">
         <v>29</v>
@@ -21556,10 +21676,10 @@
         <v>140</v>
       </c>
       <c r="C169" s="11" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="D169" s="11" t="s">
-        <v>524</v>
+        <v>630</v>
       </c>
       <c r="E169" s="12"/>
       <c r="F169" s="16" t="s">
@@ -21569,13 +21689,13 @@
         <v>23</v>
       </c>
       <c r="H169" s="22" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="I169" s="11" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="J169" s="11" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="K169" s="16">
         <f>L169*(1-0.22)</f>
@@ -21591,7 +21711,7 @@
         <v>27</v>
       </c>
       <c r="O169" s="21" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="P169" s="20" t="s">
         <v>29</v>
@@ -21602,10 +21722,10 @@
         <v>141</v>
       </c>
       <c r="C170" s="11" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="D170" s="11" t="s">
-        <v>524</v>
+        <v>631</v>
       </c>
       <c r="E170" s="12"/>
       <c r="F170" s="16" t="s">
@@ -21615,13 +21735,13 @@
         <v>23</v>
       </c>
       <c r="H170" s="22" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="I170" s="11" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="J170" s="11" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="K170" s="16">
         <f>L170*(1-0.22)</f>
@@ -21637,7 +21757,7 @@
         <v>27</v>
       </c>
       <c r="O170" s="21" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="P170" s="20" t="s">
         <v>29</v>
@@ -21648,10 +21768,10 @@
         <v>142</v>
       </c>
       <c r="C171" s="11" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="D171" s="11" t="s">
-        <v>524</v>
+        <v>632</v>
       </c>
       <c r="E171" s="12"/>
       <c r="F171" s="16" t="s">
@@ -21661,13 +21781,13 @@
         <v>23</v>
       </c>
       <c r="H171" s="22" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="I171" s="11" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="J171" s="11" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="K171" s="16">
         <f>L171*(1-0.22)</f>
@@ -21683,32 +21803,32 @@
         <v>27</v>
       </c>
       <c r="O171" s="21" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="P171" s="20" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="172" spans="2:20" ht="50.1" customHeight="1">
-      <c r="B172" s="63" t="s">
-        <v>536</v>
-      </c>
-      <c r="C172" s="64"/>
-      <c r="D172" s="64"/>
-      <c r="E172" s="64"/>
-      <c r="F172" s="64"/>
-      <c r="G172" s="64"/>
-      <c r="H172" s="64"/>
-      <c r="I172" s="64"/>
-      <c r="J172" s="64"/>
-      <c r="K172" s="64"/>
-      <c r="L172" s="64"/>
-      <c r="M172" s="65"/>
+      <c r="B172" s="90" t="s">
+        <v>532</v>
+      </c>
+      <c r="C172" s="91"/>
+      <c r="D172" s="91"/>
+      <c r="E172" s="91"/>
+      <c r="F172" s="91"/>
+      <c r="G172" s="91"/>
+      <c r="H172" s="91"/>
+      <c r="I172" s="91"/>
+      <c r="J172" s="91"/>
+      <c r="K172" s="91"/>
+      <c r="L172" s="91"/>
+      <c r="M172" s="92"/>
       <c r="N172" s="19" t="s">
         <v>27</v>
       </c>
       <c r="O172" s="21" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="P172" s="20" t="s">
         <v>29</v>
@@ -21719,26 +21839,26 @@
         <v>143</v>
       </c>
       <c r="C173" s="11" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="D173" s="11" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="E173" s="12"/>
       <c r="F173" s="11" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="G173" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H173" s="22" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="I173" s="11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J173" s="11" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="K173" s="16">
         <f>L173*(1-0.22)</f>
@@ -21754,7 +21874,7 @@
         <v>27</v>
       </c>
       <c r="O173" s="21" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="P173" s="20" t="s">
         <v>29</v>
@@ -21765,26 +21885,26 @@
         <v>144</v>
       </c>
       <c r="C174" s="11" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="D174" s="11" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="E174" s="12"/>
       <c r="F174" s="11" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="G174" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H174" s="22" t="s">
+        <v>537</v>
+      </c>
+      <c r="I174" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="J174" s="11" t="s">
         <v>541</v>
-      </c>
-      <c r="I174" s="11" t="s">
-        <v>291</v>
-      </c>
-      <c r="J174" s="11" t="s">
-        <v>545</v>
       </c>
       <c r="K174" s="16">
         <f>L174*(1-0.22)</f>
@@ -21800,7 +21920,7 @@
         <v>27</v>
       </c>
       <c r="O174" s="21" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="P174" s="20" t="s">
         <v>29</v>
@@ -21811,26 +21931,26 @@
         <v>145</v>
       </c>
       <c r="C175" s="11" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="D175" s="11" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="E175" s="12"/>
       <c r="F175" s="11" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="G175" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H175" s="22" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="I175" s="11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J175" s="11" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="K175" s="16">
         <f>L175*(1-0.22)</f>
@@ -21846,7 +21966,7 @@
         <v>27</v>
       </c>
       <c r="O175" s="21" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="P175" s="20" t="s">
         <v>29</v>
@@ -21857,26 +21977,26 @@
         <v>146</v>
       </c>
       <c r="C176" s="28" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="D176" s="28" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="E176" s="41"/>
       <c r="F176" s="28" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="G176" s="28" t="s">
         <v>23</v>
       </c>
       <c r="H176" s="43" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="I176" s="28" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J176" s="28" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="K176" s="40">
         <f>L176*(1-0.22)</f>
@@ -21892,7 +22012,7 @@
         <v>27</v>
       </c>
       <c r="O176" s="21" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="P176" s="20" t="s">
         <v>29</v>
@@ -21903,25 +22023,25 @@
       <c r="T176" s="32"/>
     </row>
     <row r="177" spans="2:20" ht="50.1" customHeight="1">
-      <c r="B177" s="63" t="s">
-        <v>552</v>
-      </c>
-      <c r="C177" s="64"/>
-      <c r="D177" s="64"/>
-      <c r="E177" s="64"/>
-      <c r="F177" s="64"/>
-      <c r="G177" s="64"/>
-      <c r="H177" s="64"/>
-      <c r="I177" s="64"/>
-      <c r="J177" s="64"/>
-      <c r="K177" s="64"/>
-      <c r="L177" s="64"/>
-      <c r="M177" s="65"/>
+      <c r="B177" s="90" t="s">
+        <v>548</v>
+      </c>
+      <c r="C177" s="91"/>
+      <c r="D177" s="91"/>
+      <c r="E177" s="91"/>
+      <c r="F177" s="91"/>
+      <c r="G177" s="91"/>
+      <c r="H177" s="91"/>
+      <c r="I177" s="91"/>
+      <c r="J177" s="91"/>
+      <c r="K177" s="91"/>
+      <c r="L177" s="91"/>
+      <c r="M177" s="92"/>
       <c r="N177" s="19" t="s">
         <v>27</v>
       </c>
       <c r="O177" s="21" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="P177" s="20" t="s">
         <v>29</v>
@@ -21932,26 +22052,26 @@
         <v>147</v>
       </c>
       <c r="C178" s="11" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="D178" s="11" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="E178" s="12"/>
       <c r="F178" s="11" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="G178" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H178" s="22" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="I178" s="11" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="J178" s="11" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="K178" s="16">
         <f>L178*(1-0.22)</f>
@@ -21967,7 +22087,7 @@
         <v>27</v>
       </c>
       <c r="O178" s="21" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="P178" s="20" t="s">
         <v>29</v>
@@ -21978,26 +22098,26 @@
         <v>148</v>
       </c>
       <c r="C179" s="11" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="D179" s="11" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="E179" s="12"/>
       <c r="F179" s="11" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="G179" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H179" s="22" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="I179" s="11" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="J179" s="11" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="K179" s="16">
         <f>L179*(1-0.22)</f>
@@ -22013,7 +22133,7 @@
         <v>27</v>
       </c>
       <c r="O179" s="21" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="P179" s="20" t="s">
         <v>29</v>
@@ -22024,26 +22144,26 @@
         <v>149</v>
       </c>
       <c r="C180" s="11" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="D180" s="11" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="E180" s="12"/>
       <c r="F180" s="11" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="G180" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H180" s="22" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="I180" s="11" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="J180" s="11" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="K180" s="16">
         <f>L180*(1-0.22)</f>
@@ -22059,7 +22179,7 @@
         <v>27</v>
       </c>
       <c r="O180" s="21" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="P180" s="20" t="s">
         <v>29</v>
@@ -22070,26 +22190,26 @@
         <v>150</v>
       </c>
       <c r="C181" s="11" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="D181" s="11" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="E181" s="12"/>
       <c r="F181" s="11" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="G181" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H181" s="22" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="I181" s="11" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="J181" s="11" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="K181" s="16">
         <f>L181*(1-0.22)</f>
@@ -22105,7 +22225,7 @@
         <v>27</v>
       </c>
       <c r="O181" s="21" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="P181" s="20" t="s">
         <v>29</v>
@@ -22116,26 +22236,26 @@
         <v>151</v>
       </c>
       <c r="C182" s="11" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="D182" s="11" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="E182" s="12"/>
       <c r="F182" s="11" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="G182" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H182" s="22" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="I182" s="11" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="J182" s="11" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="K182" s="16">
         <f>L182*(1-0.22)</f>
@@ -22151,32 +22271,32 @@
         <v>27</v>
       </c>
       <c r="O182" s="21" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="P182" s="20" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="183" spans="2:20" ht="50.1" customHeight="1">
-      <c r="B183" s="63" t="s">
-        <v>573</v>
-      </c>
-      <c r="C183" s="64"/>
-      <c r="D183" s="64"/>
-      <c r="E183" s="64"/>
-      <c r="F183" s="64"/>
-      <c r="G183" s="64"/>
-      <c r="H183" s="64"/>
-      <c r="I183" s="64"/>
-      <c r="J183" s="64"/>
-      <c r="K183" s="64"/>
-      <c r="L183" s="64"/>
-      <c r="M183" s="65"/>
+      <c r="B183" s="90" t="s">
+        <v>569</v>
+      </c>
+      <c r="C183" s="91"/>
+      <c r="D183" s="91"/>
+      <c r="E183" s="91"/>
+      <c r="F183" s="91"/>
+      <c r="G183" s="91"/>
+      <c r="H183" s="91"/>
+      <c r="I183" s="91"/>
+      <c r="J183" s="91"/>
+      <c r="K183" s="91"/>
+      <c r="L183" s="91"/>
+      <c r="M183" s="92"/>
       <c r="N183" s="19" t="s">
         <v>27</v>
       </c>
       <c r="O183" s="21" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="P183" s="20" t="s">
         <v>29</v>
@@ -22187,26 +22307,26 @@
         <v>152</v>
       </c>
       <c r="C184" s="11" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="D184" s="11" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="E184" s="12"/>
       <c r="F184" s="11" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="G184" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H184" s="22" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="I184" s="11" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="J184" s="11" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="K184" s="16">
         <f>L184*(1-0.22)</f>
@@ -22222,7 +22342,7 @@
         <v>27</v>
       </c>
       <c r="O184" s="21" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="P184" s="20" t="s">
         <v>29</v>
@@ -22233,26 +22353,26 @@
         <v>153</v>
       </c>
       <c r="C185" s="11" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="D185" s="11" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="E185" s="12"/>
       <c r="F185" s="11" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="G185" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H185" s="22" t="s">
+        <v>573</v>
+      </c>
+      <c r="I185" s="11" t="s">
         <v>577</v>
       </c>
-      <c r="I185" s="11" t="s">
-        <v>581</v>
-      </c>
       <c r="J185" s="11" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="K185" s="16">
         <f>L185*(1-0.22)</f>
@@ -22268,7 +22388,7 @@
         <v>27</v>
       </c>
       <c r="O185" s="21" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="P185" s="20" t="s">
         <v>29</v>
@@ -22279,26 +22399,26 @@
         <v>154</v>
       </c>
       <c r="C186" s="11" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="D186" s="11" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="E186" s="12"/>
       <c r="F186" s="11" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="G186" s="11" t="s">
         <v>23</v>
       </c>
       <c r="H186" s="22" t="s">
+        <v>573</v>
+      </c>
+      <c r="I186" s="11" t="s">
         <v>577</v>
       </c>
-      <c r="I186" s="11" t="s">
-        <v>581</v>
-      </c>
       <c r="J186" s="11" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="K186" s="16">
         <f>L186*(1-0.22)</f>
@@ -22314,32 +22434,32 @@
         <v>27</v>
       </c>
       <c r="O186" s="21" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="P186" s="20" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="187" spans="2:20" ht="50.1" customHeight="1">
-      <c r="B187" s="63" t="s">
-        <v>585</v>
-      </c>
-      <c r="C187" s="64"/>
-      <c r="D187" s="64"/>
-      <c r="E187" s="64"/>
-      <c r="F187" s="64"/>
-      <c r="G187" s="64"/>
-      <c r="H187" s="64"/>
-      <c r="I187" s="64"/>
-      <c r="J187" s="64"/>
-      <c r="K187" s="64"/>
-      <c r="L187" s="64"/>
-      <c r="M187" s="65"/>
+      <c r="B187" s="90" t="s">
+        <v>581</v>
+      </c>
+      <c r="C187" s="91"/>
+      <c r="D187" s="91"/>
+      <c r="E187" s="91"/>
+      <c r="F187" s="91"/>
+      <c r="G187" s="91"/>
+      <c r="H187" s="91"/>
+      <c r="I187" s="91"/>
+      <c r="J187" s="91"/>
+      <c r="K187" s="91"/>
+      <c r="L187" s="91"/>
+      <c r="M187" s="92"/>
       <c r="N187" s="19" t="s">
         <v>27</v>
       </c>
       <c r="O187" s="21" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="P187" s="20" t="s">
         <v>29</v>
@@ -22350,26 +22470,26 @@
         <v>155</v>
       </c>
       <c r="C188" s="28" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="D188" s="28" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="E188" s="41"/>
       <c r="F188" s="28" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="G188" s="28" t="s">
         <v>23</v>
       </c>
       <c r="H188" s="50" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="I188" s="28" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="J188" s="28" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="K188" s="40">
         <f>L188*(1-0.22)</f>
@@ -22385,7 +22505,7 @@
         <v>27</v>
       </c>
       <c r="O188" s="55" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="P188" s="56" t="s">
         <v>29</v>
@@ -23277,16 +23397,78 @@
     </row>
   </sheetData>
   <mergeCells count="98">
-    <mergeCell ref="J84:J85"/>
-    <mergeCell ref="J86:J87"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="J74:J75"/>
-    <mergeCell ref="J76:J77"/>
-    <mergeCell ref="J78:J79"/>
-    <mergeCell ref="J80:J81"/>
-    <mergeCell ref="J82:J83"/>
+    <mergeCell ref="B1:M1"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="B33:M33"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="B84:B85"/>
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="B41:M41"/>
+    <mergeCell ref="B55:M55"/>
+    <mergeCell ref="B60:M60"/>
+    <mergeCell ref="B64:M64"/>
+    <mergeCell ref="B71:M71"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C84:C85"/>
+    <mergeCell ref="B172:M172"/>
+    <mergeCell ref="B177:M177"/>
+    <mergeCell ref="B183:M183"/>
+    <mergeCell ref="B187:M187"/>
+    <mergeCell ref="B155:M155"/>
+    <mergeCell ref="B157:M157"/>
+    <mergeCell ref="B159:M159"/>
+    <mergeCell ref="B162:M162"/>
+    <mergeCell ref="B167:M167"/>
+    <mergeCell ref="B88:M88"/>
+    <mergeCell ref="B91:M91"/>
+    <mergeCell ref="B112:M112"/>
+    <mergeCell ref="B131:M131"/>
+    <mergeCell ref="B149:M149"/>
+    <mergeCell ref="E89:E90"/>
+    <mergeCell ref="F80:F81"/>
+    <mergeCell ref="C86:C87"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="E72:E73"/>
+    <mergeCell ref="E74:E75"/>
+    <mergeCell ref="E76:E77"/>
+    <mergeCell ref="E78:E79"/>
+    <mergeCell ref="E80:E81"/>
+    <mergeCell ref="E82:E83"/>
+    <mergeCell ref="E84:E85"/>
+    <mergeCell ref="E86:E87"/>
+    <mergeCell ref="C76:C77"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="C80:C81"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="H80:H81"/>
+    <mergeCell ref="F82:F83"/>
+    <mergeCell ref="F84:F85"/>
+    <mergeCell ref="F86:F87"/>
+    <mergeCell ref="G72:G73"/>
+    <mergeCell ref="G74:G75"/>
+    <mergeCell ref="G76:G77"/>
+    <mergeCell ref="G78:G79"/>
+    <mergeCell ref="G80:G81"/>
+    <mergeCell ref="G82:G83"/>
+    <mergeCell ref="G84:G85"/>
+    <mergeCell ref="G86:G87"/>
+    <mergeCell ref="F72:F73"/>
+    <mergeCell ref="F74:F75"/>
+    <mergeCell ref="F76:F77"/>
+    <mergeCell ref="F78:F79"/>
     <mergeCell ref="H82:H83"/>
     <mergeCell ref="H84:H85"/>
     <mergeCell ref="H86:H87"/>
@@ -23303,78 +23485,16 @@
     <mergeCell ref="H74:H75"/>
     <mergeCell ref="H76:H77"/>
     <mergeCell ref="H78:H79"/>
-    <mergeCell ref="H80:H81"/>
-    <mergeCell ref="F82:F83"/>
-    <mergeCell ref="F84:F85"/>
-    <mergeCell ref="F86:F87"/>
-    <mergeCell ref="G72:G73"/>
-    <mergeCell ref="G74:G75"/>
-    <mergeCell ref="G76:G77"/>
-    <mergeCell ref="G78:G79"/>
-    <mergeCell ref="G80:G81"/>
-    <mergeCell ref="G82:G83"/>
-    <mergeCell ref="G84:G85"/>
-    <mergeCell ref="G86:G87"/>
-    <mergeCell ref="F72:F73"/>
-    <mergeCell ref="F74:F75"/>
-    <mergeCell ref="F76:F77"/>
-    <mergeCell ref="F78:F79"/>
-    <mergeCell ref="F80:F81"/>
-    <mergeCell ref="C86:C87"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="E72:E73"/>
-    <mergeCell ref="E74:E75"/>
-    <mergeCell ref="E76:E77"/>
-    <mergeCell ref="E78:E79"/>
-    <mergeCell ref="E80:E81"/>
-    <mergeCell ref="E82:E83"/>
-    <mergeCell ref="E84:E85"/>
-    <mergeCell ref="E86:E87"/>
-    <mergeCell ref="C76:C77"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="C80:C81"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="C84:C85"/>
-    <mergeCell ref="B172:M172"/>
-    <mergeCell ref="B177:M177"/>
-    <mergeCell ref="B183:M183"/>
-    <mergeCell ref="B187:M187"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="B84:B85"/>
-    <mergeCell ref="B86:B87"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="B155:M155"/>
-    <mergeCell ref="B157:M157"/>
-    <mergeCell ref="B159:M159"/>
-    <mergeCell ref="B162:M162"/>
-    <mergeCell ref="B167:M167"/>
-    <mergeCell ref="B88:M88"/>
-    <mergeCell ref="B91:M91"/>
-    <mergeCell ref="B112:M112"/>
-    <mergeCell ref="B131:M131"/>
-    <mergeCell ref="B149:M149"/>
-    <mergeCell ref="E89:E90"/>
-    <mergeCell ref="B41:M41"/>
-    <mergeCell ref="B55:M55"/>
-    <mergeCell ref="B60:M60"/>
-    <mergeCell ref="B64:M64"/>
-    <mergeCell ref="B71:M71"/>
-    <mergeCell ref="B1:M1"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="B33:M33"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="J84:J85"/>
+    <mergeCell ref="J86:J87"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="J74:J75"/>
+    <mergeCell ref="J76:J77"/>
+    <mergeCell ref="J78:J79"/>
+    <mergeCell ref="J80:J81"/>
+    <mergeCell ref="J82:J83"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="10" orientation="portrait" r:id="rId1"/>
